--- a/demo_data/sectors/toptan_ticaret/sales_ledger.xlsx
+++ b/demo_data/sectors/toptan_ticaret/sales_ledger.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Maliyet</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Net Satış Tutarı</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Maliyet</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -492,37 +492,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F2" t="n">
-        <v>1512347.16</v>
+        <v>158535.33</v>
       </c>
       <c r="G2" t="n">
-        <v>181481.66</v>
+        <v>6959.94</v>
       </c>
       <c r="H2" t="n">
-        <v>1330865.5</v>
+        <v>99084.58</v>
       </c>
       <c r="I2" t="n">
-        <v>962402.74</v>
+        <v>151575.39</v>
       </c>
       <c r="J2" t="n">
-        <v>1330865.5</v>
+        <v>151575.39</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -536,32 +536,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F3" t="n">
-        <v>221826.32</v>
+        <v>111094.83</v>
       </c>
       <c r="G3" t="n">
-        <v>11091.32</v>
+        <v>1950.9</v>
       </c>
       <c r="H3" t="n">
-        <v>210735.01</v>
+        <v>75064.07000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>138641.45</v>
+        <v>109143.93</v>
       </c>
       <c r="J3" t="n">
-        <v>210735.01</v>
+        <v>109143.93</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -582,25 +582,25 @@
         <v>45662</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>21500</v>
       </c>
       <c r="F4" t="n">
-        <v>2235593.39</v>
+        <v>645551.03</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>17004.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2235593.39</v>
+        <v>426363.94</v>
       </c>
       <c r="I4" t="n">
-        <v>1476531.45</v>
+        <v>628546.58</v>
       </c>
       <c r="J4" t="n">
-        <v>2235593.39</v>
+        <v>628546.58</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,37 +609,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F5" t="n">
-        <v>138641.45</v>
+        <v>1549322.47</v>
       </c>
       <c r="G5" t="n">
-        <v>11091.32</v>
+        <v>27207.12</v>
       </c>
       <c r="H5" t="n">
-        <v>127550.13</v>
+        <v>1023273.45</v>
       </c>
       <c r="I5" t="n">
-        <v>94738.32000000001</v>
+        <v>1522115.35</v>
       </c>
       <c r="J5" t="n">
-        <v>127550.13</v>
+        <v>1522115.35</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,37 +648,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F6" t="n">
-        <v>154238.61</v>
+        <v>216184.53</v>
       </c>
       <c r="G6" t="n">
-        <v>4627.16</v>
+        <v>3796.34</v>
       </c>
       <c r="H6" t="n">
-        <v>149611.46</v>
+        <v>135115.33</v>
       </c>
       <c r="I6" t="n">
-        <v>102248.07</v>
+        <v>212388.19</v>
       </c>
       <c r="J6" t="n">
-        <v>149611.46</v>
+        <v>212388.19</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F7" t="n">
-        <v>152505.6</v>
+        <v>165741.47</v>
       </c>
       <c r="G7" t="n">
-        <v>12200.45</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>140305.15</v>
+        <v>113256.67</v>
       </c>
       <c r="I7" t="n">
-        <v>95316</v>
+        <v>165741.47</v>
       </c>
       <c r="J7" t="n">
-        <v>140305.15</v>
+        <v>165741.47</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,37 +726,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F8" t="n">
-        <v>106869.45</v>
+        <v>115298.42</v>
       </c>
       <c r="G8" t="n">
-        <v>12824.33</v>
+        <v>3037.07</v>
       </c>
       <c r="H8" t="n">
-        <v>94045.12</v>
+        <v>72061.50999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>72209.09</v>
+        <v>112261.35</v>
       </c>
       <c r="J8" t="n">
-        <v>94045.12</v>
+        <v>112261.35</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,37 +765,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F9" t="n">
-        <v>620998.16</v>
+        <v>93679.96000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>31049.91</v>
+        <v>2467.62</v>
       </c>
       <c r="H9" t="n">
-        <v>589948.26</v>
+        <v>63414.13</v>
       </c>
       <c r="I9" t="n">
-        <v>410147.62</v>
+        <v>91212.34</v>
       </c>
       <c r="J9" t="n">
-        <v>589948.26</v>
+        <v>91212.34</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,37 +804,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F10" t="n">
-        <v>1490395.59</v>
+        <v>187359.93</v>
       </c>
       <c r="G10" t="n">
-        <v>44711.87</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1445683.73</v>
+        <v>117099.95</v>
       </c>
       <c r="I10" t="n">
-        <v>984354.3</v>
+        <v>187359.93</v>
       </c>
       <c r="J10" t="n">
-        <v>1445683.73</v>
+        <v>187359.93</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F11" t="n">
-        <v>207962.18</v>
+        <v>55547.41</v>
       </c>
       <c r="G11" t="n">
-        <v>6238.87</v>
+        <v>2438.62</v>
       </c>
       <c r="H11" t="n">
-        <v>201723.31</v>
+        <v>37532.04</v>
       </c>
       <c r="I11" t="n">
-        <v>129976.36</v>
+        <v>53108.79</v>
       </c>
       <c r="J11" t="n">
-        <v>201723.31</v>
+        <v>53108.79</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -882,37 +882,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F12" t="n">
-        <v>159437.67</v>
+        <v>15613.33</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>411.27</v>
       </c>
       <c r="H12" t="n">
-        <v>159437.67</v>
+        <v>10569.02</v>
       </c>
       <c r="I12" t="n">
-        <v>108949.07</v>
+        <v>15202.06</v>
       </c>
       <c r="J12" t="n">
-        <v>159437.67</v>
+        <v>15202.06</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -921,37 +921,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F13" t="n">
-        <v>110913.16</v>
+        <v>129110.21</v>
       </c>
       <c r="G13" t="n">
-        <v>5545.66</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>105367.5</v>
+        <v>85272.78999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>69320.73</v>
+        <v>129110.21</v>
       </c>
       <c r="J13" t="n">
-        <v>105367.5</v>
+        <v>129110.21</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,37 +960,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F14" t="n">
-        <v>90116.94</v>
+        <v>160336.86</v>
       </c>
       <c r="G14" t="n">
-        <v>4505.85</v>
+        <v>4223.43</v>
       </c>
       <c r="H14" t="n">
-        <v>85611.10000000001</v>
+        <v>106290.73</v>
       </c>
       <c r="I14" t="n">
-        <v>61002.24</v>
+        <v>156113.43</v>
       </c>
       <c r="J14" t="n">
-        <v>85611.10000000001</v>
+        <v>156113.43</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F15" t="n">
-        <v>180233.89</v>
+        <v>1017268.32</v>
       </c>
       <c r="G15" t="n">
-        <v>21628.07</v>
+        <v>44659.75</v>
       </c>
       <c r="H15" t="n">
-        <v>158605.82</v>
+        <v>647352.5699999999</v>
       </c>
       <c r="I15" t="n">
-        <v>112646.18</v>
+        <v>972608.5699999999</v>
       </c>
       <c r="J15" t="n">
-        <v>158605.82</v>
+        <v>972608.5699999999</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F16" t="n">
-        <v>822605.9399999999</v>
+        <v>302658.34</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>822605.9399999999</v>
+        <v>189161.46</v>
       </c>
       <c r="I16" t="n">
-        <v>545323.04</v>
+        <v>302658.34</v>
       </c>
       <c r="J16" t="n">
-        <v>822605.9399999999</v>
+        <v>302658.34</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1089,25 +1089,25 @@
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
         <v>650</v>
       </c>
       <c r="F17" t="n">
-        <v>15019.49</v>
+        <v>85873.3</v>
       </c>
       <c r="G17" t="n">
-        <v>750.97</v>
+        <v>3769.98</v>
       </c>
       <c r="H17" t="n">
-        <v>14268.52</v>
+        <v>58129.62</v>
       </c>
       <c r="I17" t="n">
-        <v>10167.04</v>
+        <v>82103.32000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>14268.52</v>
+        <v>82103.32000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F18" t="n">
-        <v>124199.63</v>
+        <v>81969.97</v>
       </c>
       <c r="G18" t="n">
-        <v>14903.96</v>
+        <v>2159.17</v>
       </c>
       <c r="H18" t="n">
-        <v>109295.68</v>
+        <v>55487.36</v>
       </c>
       <c r="I18" t="n">
-        <v>82029.52</v>
+        <v>79810.8</v>
       </c>
       <c r="J18" t="n">
-        <v>109295.68</v>
+        <v>79810.8</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,37 +1155,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F19" t="n">
-        <v>291147.05</v>
+        <v>222189.66</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>291147.05</v>
+        <v>150128.15</v>
       </c>
       <c r="I19" t="n">
-        <v>181966.9</v>
+        <v>222189.66</v>
       </c>
       <c r="J19" t="n">
-        <v>291147.05</v>
+        <v>222189.66</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F20" t="n">
-        <v>1117796.7</v>
+        <v>739831.51</v>
       </c>
       <c r="G20" t="n">
-        <v>33533.9</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1084262.8</v>
+        <v>470801.87</v>
       </c>
       <c r="I20" t="n">
-        <v>738265.72</v>
+        <v>739831.51</v>
       </c>
       <c r="J20" t="n">
-        <v>1084262.8</v>
+        <v>739831.51</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,37 +1233,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E21" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F21" t="n">
-        <v>291147.05</v>
+        <v>630538.22</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>291147.05</v>
+        <v>420358.81</v>
       </c>
       <c r="I21" t="n">
-        <v>181966.9</v>
+        <v>630538.22</v>
       </c>
       <c r="J21" t="n">
-        <v>291147.05</v>
+        <v>630538.22</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F22" t="n">
-        <v>82607.2</v>
+        <v>1229249.26</v>
       </c>
       <c r="G22" t="n">
-        <v>6608.58</v>
+        <v>21586.42</v>
       </c>
       <c r="H22" t="n">
-        <v>75998.62</v>
+        <v>814895.58</v>
       </c>
       <c r="I22" t="n">
-        <v>55918.72</v>
+        <v>1207662.84</v>
       </c>
       <c r="J22" t="n">
-        <v>75998.62</v>
+        <v>1207662.84</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F23" t="n">
-        <v>78852.33</v>
+        <v>22218.97</v>
       </c>
       <c r="G23" t="n">
-        <v>9462.280000000001</v>
+        <v>390.18</v>
       </c>
       <c r="H23" t="n">
-        <v>69390.05</v>
+        <v>15012.81</v>
       </c>
       <c r="I23" t="n">
-        <v>53376.96</v>
+        <v>21828.79</v>
       </c>
       <c r="J23" t="n">
-        <v>69390.05</v>
+        <v>21828.79</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F24" t="n">
-        <v>2235593.39</v>
+        <v>111094.83</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1950.9</v>
       </c>
       <c r="H24" t="n">
-        <v>2235593.39</v>
+        <v>75064.07000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>1476531.45</v>
+        <v>109143.93</v>
       </c>
       <c r="J24" t="n">
-        <v>2235593.39</v>
+        <v>109143.93</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F25" t="n">
-        <v>194098.03</v>
+        <v>72061.50999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>23291.76</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>170806.27</v>
+        <v>45038.44</v>
       </c>
       <c r="I25" t="n">
-        <v>129398.69</v>
+        <v>72061.50999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>170806.27</v>
+        <v>72061.50999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F26" t="n">
-        <v>711692.78</v>
+        <v>273833.74</v>
       </c>
       <c r="G26" t="n">
-        <v>85403.13</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>626289.65</v>
+        <v>171146.09</v>
       </c>
       <c r="I26" t="n">
-        <v>452895.41</v>
+        <v>273833.74</v>
       </c>
       <c r="J26" t="n">
-        <v>626289.65</v>
+        <v>273833.74</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F27" t="n">
-        <v>55456.58</v>
+        <v>160336.86</v>
       </c>
       <c r="G27" t="n">
-        <v>6654.79</v>
+        <v>7039.05</v>
       </c>
       <c r="H27" t="n">
-        <v>48801.79</v>
+        <v>106290.73</v>
       </c>
       <c r="I27" t="n">
-        <v>34660.36</v>
+        <v>153297.81</v>
       </c>
       <c r="J27" t="n">
-        <v>48801.79</v>
+        <v>153297.81</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E28" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F28" t="n">
-        <v>363933.81</v>
+        <v>288246.04</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>363933.81</v>
+        <v>180153.78</v>
       </c>
       <c r="I28" t="n">
-        <v>242622.54</v>
+        <v>288246.04</v>
       </c>
       <c r="J28" t="n">
-        <v>363933.81</v>
+        <v>288246.04</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,37 +1545,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F29" t="n">
-        <v>88961.60000000001</v>
+        <v>427564.96</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>11262.48</v>
       </c>
       <c r="H29" t="n">
-        <v>88961.60000000001</v>
+        <v>283441.94</v>
       </c>
       <c r="I29" t="n">
-        <v>56611.93</v>
+        <v>416302.48</v>
       </c>
       <c r="J29" t="n">
-        <v>88961.60000000001</v>
+        <v>416302.48</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F30" t="n">
-        <v>106869.45</v>
+        <v>1387184.07</v>
       </c>
       <c r="G30" t="n">
-        <v>3206.08</v>
+        <v>24359.86</v>
       </c>
       <c r="H30" t="n">
-        <v>103663.37</v>
+        <v>882753.5</v>
       </c>
       <c r="I30" t="n">
-        <v>72209.09</v>
+        <v>1362824.21</v>
       </c>
       <c r="J30" t="n">
-        <v>103663.37</v>
+        <v>1362824.21</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F31" t="n">
-        <v>69320.73</v>
+        <v>166642.24</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2926.35</v>
       </c>
       <c r="H31" t="n">
-        <v>69320.73</v>
+        <v>112596.11</v>
       </c>
       <c r="I31" t="n">
-        <v>43325.45</v>
+        <v>163715.89</v>
       </c>
       <c r="J31" t="n">
-        <v>69320.73</v>
+        <v>163715.89</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F32" t="n">
-        <v>263418.76</v>
+        <v>160336.86</v>
       </c>
       <c r="G32" t="n">
-        <v>31610.25</v>
+        <v>4223.43</v>
       </c>
       <c r="H32" t="n">
-        <v>231808.51</v>
+        <v>106290.73</v>
       </c>
       <c r="I32" t="n">
-        <v>164636.72</v>
+        <v>156113.43</v>
       </c>
       <c r="J32" t="n">
-        <v>231808.51</v>
+        <v>156113.43</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F33" t="n">
-        <v>308477.23</v>
+        <v>1942057.7</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>51155.71</v>
       </c>
       <c r="H33" t="n">
-        <v>308477.23</v>
+        <v>1235854.9</v>
       </c>
       <c r="I33" t="n">
-        <v>204496.14</v>
+        <v>1890901.99</v>
       </c>
       <c r="J33" t="n">
-        <v>308477.23</v>
+        <v>1890901.99</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F34" t="n">
-        <v>277282.9</v>
+        <v>1387184.07</v>
       </c>
       <c r="G34" t="n">
-        <v>33273.95</v>
+        <v>24359.86</v>
       </c>
       <c r="H34" t="n">
-        <v>244008.95</v>
+        <v>882753.5</v>
       </c>
       <c r="I34" t="n">
-        <v>173301.81</v>
+        <v>1362824.21</v>
       </c>
       <c r="J34" t="n">
-        <v>244008.95</v>
+        <v>1362824.21</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1784,32 +1784,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F35" t="n">
-        <v>2359793.02</v>
+        <v>230596.83</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2359793.02</v>
+        <v>144123.02</v>
       </c>
       <c r="I35" t="n">
-        <v>1558560.97</v>
+        <v>230596.83</v>
       </c>
       <c r="J35" t="n">
-        <v>2359793.02</v>
+        <v>230596.83</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1823,32 +1823,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F36" t="n">
-        <v>2608192.29</v>
+        <v>273833.74</v>
       </c>
       <c r="G36" t="n">
-        <v>78245.77</v>
+        <v>4808.7</v>
       </c>
       <c r="H36" t="n">
-        <v>2529946.52</v>
+        <v>171146.09</v>
       </c>
       <c r="I36" t="n">
-        <v>1722620.02</v>
+        <v>269025.04</v>
       </c>
       <c r="J36" t="n">
-        <v>2529946.52</v>
+        <v>269025.04</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1869,25 +1869,25 @@
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E37" t="n">
         <v>15400</v>
       </c>
       <c r="F37" t="n">
-        <v>1957155.15</v>
+        <v>2127015.58</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>37351.79</v>
       </c>
       <c r="H37" t="n">
-        <v>1957155.15</v>
+        <v>1353555.37</v>
       </c>
       <c r="I37" t="n">
-        <v>1245462.37</v>
+        <v>2089663.79</v>
       </c>
       <c r="J37" t="n">
-        <v>1957155.15</v>
+        <v>2089663.79</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1896,37 +1896,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F38" t="n">
-        <v>1241996.33</v>
+        <v>129710.72</v>
       </c>
       <c r="G38" t="n">
-        <v>149039.56</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1092956.77</v>
+        <v>81069.2</v>
       </c>
       <c r="I38" t="n">
-        <v>820295.25</v>
+        <v>129710.72</v>
       </c>
       <c r="J38" t="n">
-        <v>1092956.77</v>
+        <v>129710.72</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E39" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F39" t="n">
-        <v>154238.61</v>
+        <v>222189.66</v>
       </c>
       <c r="G39" t="n">
-        <v>7711.93</v>
+        <v>5852.69</v>
       </c>
       <c r="H39" t="n">
-        <v>146526.68</v>
+        <v>150128.15</v>
       </c>
       <c r="I39" t="n">
-        <v>102248.07</v>
+        <v>216336.97</v>
       </c>
       <c r="J39" t="n">
-        <v>146526.68</v>
+        <v>216336.97</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1986,25 +1986,25 @@
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E40" t="n">
         <v>15400</v>
       </c>
       <c r="F40" t="n">
-        <v>1868193.55</v>
+        <v>2311973.46</v>
       </c>
       <c r="G40" t="n">
-        <v>93409.67999999999</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1774783.87</v>
+        <v>1471255.84</v>
       </c>
       <c r="I40" t="n">
-        <v>1188850.44</v>
+        <v>2311973.46</v>
       </c>
       <c r="J40" t="n">
-        <v>1774783.87</v>
+        <v>2311973.46</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F41" t="n">
-        <v>1334423.96</v>
+        <v>31226.65</v>
       </c>
       <c r="G41" t="n">
-        <v>40032.72</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1294391.24</v>
+        <v>21138.04</v>
       </c>
       <c r="I41" t="n">
-        <v>849178.89</v>
+        <v>31226.65</v>
       </c>
       <c r="J41" t="n">
-        <v>1294391.24</v>
+        <v>31226.65</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E42" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F42" t="n">
-        <v>221826.32</v>
+        <v>2034536.64</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>221826.32</v>
+        <v>1294705.14</v>
       </c>
       <c r="I42" t="n">
-        <v>138641.45</v>
+        <v>2034536.64</v>
       </c>
       <c r="J42" t="n">
-        <v>221826.32</v>
+        <v>2034536.64</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E43" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F43" t="n">
-        <v>263418.76</v>
+        <v>529652.1</v>
       </c>
       <c r="G43" t="n">
-        <v>7902.56</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>255516.19</v>
+        <v>353101.4</v>
       </c>
       <c r="I43" t="n">
-        <v>164636.72</v>
+        <v>529652.1</v>
       </c>
       <c r="J43" t="n">
-        <v>255516.19</v>
+        <v>529652.1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F44" t="n">
-        <v>2046116.74</v>
+        <v>258220.41</v>
       </c>
       <c r="G44" t="n">
-        <v>61383.5</v>
+        <v>11336.3</v>
       </c>
       <c r="H44" t="n">
-        <v>1984733.24</v>
+        <v>170545.57</v>
       </c>
       <c r="I44" t="n">
-        <v>1302074.29</v>
+        <v>246884.11</v>
       </c>
       <c r="J44" t="n">
-        <v>1984733.24</v>
+        <v>246884.11</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,37 +2169,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F45" t="n">
-        <v>124777.31</v>
+        <v>160336.86</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2815.62</v>
       </c>
       <c r="H45" t="n">
-        <v>124777.31</v>
+        <v>106290.73</v>
       </c>
       <c r="I45" t="n">
-        <v>77985.82000000001</v>
+        <v>157521.24</v>
       </c>
       <c r="J45" t="n">
-        <v>124777.31</v>
+        <v>157521.24</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F46" t="n">
-        <v>213738.9</v>
+        <v>86473.81</v>
       </c>
       <c r="G46" t="n">
-        <v>25648.67</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>188090.23</v>
+        <v>54046.13</v>
       </c>
       <c r="I46" t="n">
-        <v>144418.18</v>
+        <v>86473.81</v>
       </c>
       <c r="J46" t="n">
-        <v>188090.23</v>
+        <v>86473.81</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E47" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F47" t="n">
-        <v>2224039.94</v>
+        <v>66356.64</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2913.17</v>
       </c>
       <c r="H47" t="n">
-        <v>2224039.94</v>
+        <v>44918.34</v>
       </c>
       <c r="I47" t="n">
-        <v>1415298.14</v>
+        <v>63443.47</v>
       </c>
       <c r="J47" t="n">
-        <v>2224039.94</v>
+        <v>63443.47</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F48" t="n">
-        <v>30038.98</v>
+        <v>554873.63</v>
       </c>
       <c r="G48" t="n">
-        <v>3604.68</v>
+        <v>9743.940000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>26434.3</v>
+        <v>353101.4</v>
       </c>
       <c r="I48" t="n">
-        <v>20334.08</v>
+        <v>545129.6899999999</v>
       </c>
       <c r="J48" t="n">
-        <v>26434.3</v>
+        <v>545129.6899999999</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="D49" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F49" t="n">
-        <v>1957155.15</v>
+        <v>1291102.06</v>
       </c>
       <c r="G49" t="n">
-        <v>234858.62</v>
+        <v>22672.6</v>
       </c>
       <c r="H49" t="n">
-        <v>1722296.53</v>
+        <v>852727.87</v>
       </c>
       <c r="I49" t="n">
-        <v>1245462.37</v>
+        <v>1268429.46</v>
       </c>
       <c r="J49" t="n">
-        <v>1722296.53</v>
+        <v>1268429.46</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2369,32 +2369,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E50" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="F50" t="n">
-        <v>1079670.3</v>
+        <v>378322.93</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1079670.3</v>
+        <v>252215.29</v>
       </c>
       <c r="I50" t="n">
-        <v>715736.49</v>
+        <v>378322.93</v>
       </c>
       <c r="J50" t="n">
-        <v>1079670.3</v>
+        <v>378322.93</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E51" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F51" t="n">
-        <v>106869.45</v>
+        <v>158535.32</v>
       </c>
       <c r="G51" t="n">
-        <v>5343.47</v>
+        <v>4175.98</v>
       </c>
       <c r="H51" t="n">
-        <v>101525.98</v>
+        <v>108332.47</v>
       </c>
       <c r="I51" t="n">
-        <v>72209.09</v>
+        <v>154359.34</v>
       </c>
       <c r="J51" t="n">
-        <v>101525.98</v>
+        <v>154359.34</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,7 +2442,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2454,25 +2454,25 @@
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
         <v>650</v>
       </c>
       <c r="F52" t="n">
-        <v>90116.94</v>
+        <v>11710</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>308.45</v>
       </c>
       <c r="H52" t="n">
-        <v>90116.94</v>
+        <v>7926.77</v>
       </c>
       <c r="I52" t="n">
-        <v>61002.24</v>
+        <v>11401.55</v>
       </c>
       <c r="J52" t="n">
-        <v>90116.94</v>
+        <v>11401.55</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2493,25 +2493,25 @@
         <v>45761</v>
       </c>
       <c r="D53" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E53" t="n">
         <v>15400</v>
       </c>
       <c r="F53" t="n">
-        <v>978577.5699999999</v>
+        <v>1664620.89</v>
       </c>
       <c r="G53" t="n">
-        <v>117429.31</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>861148.26</v>
+        <v>1059304.2</v>
       </c>
       <c r="I53" t="n">
-        <v>622731.1800000001</v>
+        <v>1664620.89</v>
       </c>
       <c r="J53" t="n">
-        <v>861148.26</v>
+        <v>1664620.89</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E54" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F54" t="n">
-        <v>359890.1</v>
+        <v>85873.3</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1507.99</v>
       </c>
       <c r="H54" t="n">
-        <v>359890.1</v>
+        <v>58129.62</v>
       </c>
       <c r="I54" t="n">
-        <v>238578.83</v>
+        <v>84365.31</v>
       </c>
       <c r="J54" t="n">
-        <v>359890.1</v>
+        <v>84365.31</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E55" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F55" t="n">
-        <v>63832.83</v>
+        <v>302658.34</v>
       </c>
       <c r="G55" t="n">
-        <v>5106.63</v>
+        <v>5314.88</v>
       </c>
       <c r="H55" t="n">
-        <v>58726.21</v>
+        <v>189161.46</v>
       </c>
       <c r="I55" t="n">
-        <v>43209.92</v>
+        <v>297343.46</v>
       </c>
       <c r="J55" t="n">
-        <v>58726.21</v>
+        <v>297343.46</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,37 +2598,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E56" t="n">
-        <v>15400</v>
+        <v>1200</v>
       </c>
       <c r="F56" t="n">
-        <v>533769.59</v>
+        <v>115298.42</v>
       </c>
       <c r="G56" t="n">
-        <v>16013.09</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>517756.5</v>
+        <v>78787.25</v>
       </c>
       <c r="I56" t="n">
-        <v>339671.55</v>
+        <v>115298.42</v>
       </c>
       <c r="J56" t="n">
-        <v>517756.5</v>
+        <v>115298.42</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E57" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F57" t="n">
-        <v>1241996.33</v>
+        <v>78066.64</v>
       </c>
       <c r="G57" t="n">
-        <v>149039.56</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1092956.77</v>
+        <v>52845.11</v>
       </c>
       <c r="I57" t="n">
-        <v>820295.25</v>
+        <v>78066.64</v>
       </c>
       <c r="J57" t="n">
-        <v>1092956.77</v>
+        <v>78066.64</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E58" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F58" t="n">
-        <v>15019.49</v>
+        <v>529652.1</v>
       </c>
       <c r="G58" t="n">
-        <v>750.97</v>
+        <v>13951.56</v>
       </c>
       <c r="H58" t="n">
-        <v>14268.52</v>
+        <v>353101.4</v>
       </c>
       <c r="I58" t="n">
-        <v>10167.04</v>
+        <v>515700.54</v>
       </c>
       <c r="J58" t="n">
-        <v>14268.52</v>
+        <v>515700.54</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E59" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F59" t="n">
-        <v>1285321.78</v>
+        <v>1942057.7</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>51155.71</v>
       </c>
       <c r="H59" t="n">
-        <v>1285321.78</v>
+        <v>1235854.9</v>
       </c>
       <c r="I59" t="n">
-        <v>852067.25</v>
+        <v>1890901.99</v>
       </c>
       <c r="J59" t="n">
-        <v>1285321.78</v>
+        <v>1890901.99</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,37 +2754,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F60" t="n">
-        <v>249554.61</v>
+        <v>106891.24</v>
       </c>
       <c r="G60" t="n">
-        <v>7486.64</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>242067.97</v>
+        <v>70860.49000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>155971.63</v>
+        <v>106891.24</v>
       </c>
       <c r="J60" t="n">
-        <v>242067.97</v>
+        <v>106891.24</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,37 +2793,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F61" t="n">
-        <v>13864.15</v>
+        <v>516440.82</v>
       </c>
       <c r="G61" t="n">
-        <v>415.92</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>13448.22</v>
+        <v>341091.15</v>
       </c>
       <c r="I61" t="n">
-        <v>8665.09</v>
+        <v>516440.82</v>
       </c>
       <c r="J61" t="n">
-        <v>13448.22</v>
+        <v>516440.82</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,37 +2832,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E62" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F62" t="n">
-        <v>363933.81</v>
+        <v>694793.0600000001</v>
       </c>
       <c r="G62" t="n">
-        <v>10918.01</v>
+        <v>18301.53</v>
       </c>
       <c r="H62" t="n">
-        <v>353015.79</v>
+        <v>460593.15</v>
       </c>
       <c r="I62" t="n">
-        <v>242622.54</v>
+        <v>676491.53</v>
       </c>
       <c r="J62" t="n">
-        <v>353015.79</v>
+        <v>676491.53</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,12 +2871,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -2886,22 +2886,22 @@
         <v>19</v>
       </c>
       <c r="E63" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F63" t="n">
-        <v>1690270.35</v>
+        <v>273833.74</v>
       </c>
       <c r="G63" t="n">
-        <v>84513.52</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1605756.84</v>
+        <v>171146.09</v>
       </c>
       <c r="I63" t="n">
-        <v>1075626.59</v>
+        <v>273833.74</v>
       </c>
       <c r="J63" t="n">
-        <v>1605756.84</v>
+        <v>273833.74</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,37 +2910,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E64" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F64" t="n">
-        <v>15019.49</v>
+        <v>302658.34</v>
       </c>
       <c r="G64" t="n">
-        <v>1802.34</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>13217.15</v>
+        <v>189161.46</v>
       </c>
       <c r="I64" t="n">
-        <v>10167.04</v>
+        <v>302658.34</v>
       </c>
       <c r="J64" t="n">
-        <v>13217.15</v>
+        <v>302658.34</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2961,25 +2961,25 @@
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E65" t="n">
         <v>21500</v>
       </c>
       <c r="F65" t="n">
-        <v>124199.63</v>
+        <v>2582204.12</v>
       </c>
       <c r="G65" t="n">
-        <v>9935.969999999999</v>
+        <v>68017.8</v>
       </c>
       <c r="H65" t="n">
-        <v>114263.66</v>
+        <v>1705455.74</v>
       </c>
       <c r="I65" t="n">
-        <v>82029.52</v>
+        <v>2514186.32</v>
       </c>
       <c r="J65" t="n">
-        <v>114263.66</v>
+        <v>2514186.32</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E66" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F66" t="n">
-        <v>75097.45</v>
+        <v>255518.11</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>4487.07</v>
       </c>
       <c r="H66" t="n">
-        <v>75097.45</v>
+        <v>172647.37</v>
       </c>
       <c r="I66" t="n">
-        <v>50835.2</v>
+        <v>251031.04</v>
       </c>
       <c r="J66" t="n">
-        <v>75097.45</v>
+        <v>251031.04</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E67" t="n">
-        <v>4200</v>
+        <v>21500</v>
       </c>
       <c r="F67" t="n">
-        <v>509507.33</v>
+        <v>1936653.09</v>
       </c>
       <c r="G67" t="n">
-        <v>25475.37</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>484031.96</v>
+        <v>1279091.81</v>
       </c>
       <c r="I67" t="n">
-        <v>339671.55</v>
+        <v>1936653.09</v>
       </c>
       <c r="J67" t="n">
-        <v>484031.96</v>
+        <v>1936653.09</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F68" t="n">
-        <v>1868193.55</v>
+        <v>15613.33</v>
       </c>
       <c r="G68" t="n">
-        <v>93409.67999999999</v>
+        <v>274.18</v>
       </c>
       <c r="H68" t="n">
-        <v>1774783.87</v>
+        <v>10569.02</v>
       </c>
       <c r="I68" t="n">
-        <v>1188850.44</v>
+        <v>15339.15</v>
       </c>
       <c r="J68" t="n">
-        <v>1774783.87</v>
+        <v>15339.15</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,12 +3105,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -3120,22 +3120,22 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F69" t="n">
-        <v>102825.74</v>
+        <v>7806.66</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>205.64</v>
       </c>
       <c r="H69" t="n">
-        <v>102825.74</v>
+        <v>5284.51</v>
       </c>
       <c r="I69" t="n">
-        <v>68165.38</v>
+        <v>7601.02</v>
       </c>
       <c r="J69" t="n">
-        <v>102825.74</v>
+        <v>7601.02</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -3159,22 +3159,22 @@
         <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F70" t="n">
-        <v>496798.53</v>
+        <v>28824.6</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>759.27</v>
       </c>
       <c r="H70" t="n">
-        <v>496798.53</v>
+        <v>19696.81</v>
       </c>
       <c r="I70" t="n">
-        <v>328118.1</v>
+        <v>28065.33</v>
       </c>
       <c r="J70" t="n">
-        <v>496798.53</v>
+        <v>28065.33</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E71" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F71" t="n">
-        <v>668367.33</v>
+        <v>151329.17</v>
       </c>
       <c r="G71" t="n">
-        <v>33418.37</v>
+        <v>6643.6</v>
       </c>
       <c r="H71" t="n">
-        <v>634948.96</v>
+        <v>103408.27</v>
       </c>
       <c r="I71" t="n">
-        <v>443074.97</v>
+        <v>144685.57</v>
       </c>
       <c r="J71" t="n">
-        <v>634948.96</v>
+        <v>144685.57</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E72" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F72" t="n">
-        <v>263418.76</v>
+        <v>122204.31</v>
       </c>
       <c r="G72" t="n">
-        <v>31610.25</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>231808.51</v>
+        <v>82570.48</v>
       </c>
       <c r="I72" t="n">
-        <v>164636.72</v>
+        <v>122204.31</v>
       </c>
       <c r="J72" t="n">
-        <v>231808.51</v>
+        <v>122204.31</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,37 +3261,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F73" t="n">
-        <v>719780.2</v>
+        <v>21618.45</v>
       </c>
       <c r="G73" t="n">
-        <v>86373.62</v>
+        <v>949.09</v>
       </c>
       <c r="H73" t="n">
-        <v>633406.5699999999</v>
+        <v>14772.61</v>
       </c>
       <c r="I73" t="n">
-        <v>477157.66</v>
+        <v>20669.36</v>
       </c>
       <c r="J73" t="n">
-        <v>633406.5699999999</v>
+        <v>20669.36</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,37 +3300,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="D74" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F74" t="n">
-        <v>2483992.66</v>
+        <v>57649.21</v>
       </c>
       <c r="G74" t="n">
-        <v>124199.63</v>
+        <v>1012.36</v>
       </c>
       <c r="H74" t="n">
-        <v>2359793.02</v>
+        <v>39393.63</v>
       </c>
       <c r="I74" t="n">
-        <v>1640590.5</v>
+        <v>56636.85</v>
       </c>
       <c r="J74" t="n">
-        <v>2359793.02</v>
+        <v>56636.85</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E75" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F75" t="n">
-        <v>245799.74</v>
+        <v>1068912.4</v>
       </c>
       <c r="G75" t="n">
-        <v>7373.99</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>238425.75</v>
+        <v>708604.85</v>
       </c>
       <c r="I75" t="n">
-        <v>166080.9</v>
+        <v>1068912.4</v>
       </c>
       <c r="J75" t="n">
-        <v>238425.75</v>
+        <v>1068912.4</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F76" t="n">
-        <v>1862994.49</v>
+        <v>267228.1</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>11731.75</v>
       </c>
       <c r="H76" t="n">
-        <v>1862994.49</v>
+        <v>177151.21</v>
       </c>
       <c r="I76" t="n">
-        <v>1230442.87</v>
+        <v>255496.35</v>
       </c>
       <c r="J76" t="n">
-        <v>1862994.49</v>
+        <v>255496.35</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,12 +3417,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -3432,22 +3432,22 @@
         <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F77" t="n">
-        <v>15019.49</v>
+        <v>213782.48</v>
       </c>
       <c r="G77" t="n">
-        <v>1802.34</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>13217.15</v>
+        <v>141720.97</v>
       </c>
       <c r="I77" t="n">
-        <v>10167.04</v>
+        <v>213782.48</v>
       </c>
       <c r="J77" t="n">
-        <v>13217.15</v>
+        <v>213782.48</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F78" t="n">
-        <v>7509.75</v>
+        <v>133313.79</v>
       </c>
       <c r="G78" t="n">
-        <v>375.49</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>7134.26</v>
+        <v>90076.89</v>
       </c>
       <c r="I78" t="n">
-        <v>5083.52</v>
+        <v>133313.79</v>
       </c>
       <c r="J78" t="n">
-        <v>7134.26</v>
+        <v>133313.79</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F79" t="n">
-        <v>27728.29</v>
+        <v>3903.33</v>
       </c>
       <c r="G79" t="n">
-        <v>1386.41</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>26341.88</v>
+        <v>2642.26</v>
       </c>
       <c r="I79" t="n">
-        <v>18947.66</v>
+        <v>3903.33</v>
       </c>
       <c r="J79" t="n">
-        <v>26341.88</v>
+        <v>3903.33</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,37 +3534,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F80" t="n">
-        <v>145573.52</v>
+        <v>55547.41</v>
       </c>
       <c r="G80" t="n">
-        <v>17468.82</v>
+        <v>1463.17</v>
       </c>
       <c r="H80" t="n">
-        <v>128104.7</v>
+        <v>37532.04</v>
       </c>
       <c r="I80" t="n">
-        <v>99475.24000000001</v>
+        <v>54084.24</v>
       </c>
       <c r="J80" t="n">
-        <v>128104.7</v>
+        <v>54084.24</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E81" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F81" t="n">
-        <v>21373.89</v>
+        <v>605316.6899999999</v>
       </c>
       <c r="G81" t="n">
-        <v>641.22</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>20732.67</v>
+        <v>403544.46</v>
       </c>
       <c r="I81" t="n">
-        <v>14441.82</v>
+        <v>605316.6899999999</v>
       </c>
       <c r="J81" t="n">
-        <v>20732.67</v>
+        <v>605316.6899999999</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E82" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F82" t="n">
-        <v>976844.55</v>
+        <v>3227755.15</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>56681.5</v>
       </c>
       <c r="H82" t="n">
-        <v>976844.55</v>
+        <v>2131819.68</v>
       </c>
       <c r="I82" t="n">
-        <v>647571.11</v>
+        <v>3171073.65</v>
       </c>
       <c r="J82" t="n">
-        <v>976844.55</v>
+        <v>3171073.65</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E83" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F83" t="n">
-        <v>131709.38</v>
+        <v>378322.93</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>16609</v>
       </c>
       <c r="H83" t="n">
-        <v>131709.38</v>
+        <v>252215.29</v>
       </c>
       <c r="I83" t="n">
-        <v>90001.41</v>
+        <v>361713.93</v>
       </c>
       <c r="J83" t="n">
-        <v>131709.38</v>
+        <v>361713.93</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E84" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F84" t="n">
-        <v>76252.8</v>
+        <v>266627.59</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>11705.39</v>
       </c>
       <c r="H84" t="n">
-        <v>76252.8</v>
+        <v>180153.78</v>
       </c>
       <c r="I84" t="n">
-        <v>52106.08</v>
+        <v>254922.2</v>
       </c>
       <c r="J84" t="n">
-        <v>76252.8</v>
+        <v>254922.2</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E85" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F85" t="n">
-        <v>96182.50999999999</v>
+        <v>2711314.33</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>96182.50999999999</v>
+        <v>1790728.53</v>
       </c>
       <c r="I85" t="n">
-        <v>64988.18</v>
+        <v>2711314.33</v>
       </c>
       <c r="J85" t="n">
-        <v>96182.50999999999</v>
+        <v>2711314.33</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E86" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F86" t="n">
-        <v>533769.59</v>
+        <v>1678432.68</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>44211.57</v>
       </c>
       <c r="H86" t="n">
-        <v>533769.59</v>
+        <v>1108546.23</v>
       </c>
       <c r="I86" t="n">
-        <v>339671.55</v>
+        <v>1634221.11</v>
       </c>
       <c r="J86" t="n">
-        <v>533769.59</v>
+        <v>1634221.11</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3812,32 +3812,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E87" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F87" t="n">
-        <v>53434.73</v>
+        <v>403544.46</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>10629.76</v>
       </c>
       <c r="H87" t="n">
-        <v>53434.73</v>
+        <v>269029.64</v>
       </c>
       <c r="I87" t="n">
-        <v>36104.54</v>
+        <v>392914.7</v>
       </c>
       <c r="J87" t="n">
-        <v>53434.73</v>
+        <v>392914.7</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E88" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F88" t="n">
-        <v>131709.38</v>
+        <v>277436.81</v>
       </c>
       <c r="G88" t="n">
-        <v>3951.28</v>
+        <v>12179.93</v>
       </c>
       <c r="H88" t="n">
-        <v>127758.1</v>
+        <v>184957.88</v>
       </c>
       <c r="I88" t="n">
-        <v>90001.41</v>
+        <v>265256.88</v>
       </c>
       <c r="J88" t="n">
-        <v>127758.1</v>
+        <v>265256.88</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,37 +3885,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="F89" t="n">
-        <v>462715.84</v>
+        <v>126107.64</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>2214.53</v>
       </c>
       <c r="H89" t="n">
-        <v>462715.84</v>
+        <v>84071.75999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>306744.21</v>
+        <v>123893.11</v>
       </c>
       <c r="J89" t="n">
-        <v>462715.84</v>
+        <v>123893.11</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E90" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F90" t="n">
-        <v>235690.47</v>
+        <v>50743.31</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>2227.71</v>
       </c>
       <c r="H90" t="n">
-        <v>235690.47</v>
+        <v>34349.32</v>
       </c>
       <c r="I90" t="n">
-        <v>147306.54</v>
+        <v>48515.6</v>
       </c>
       <c r="J90" t="n">
-        <v>235690.47</v>
+        <v>48515.6</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E91" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F91" t="n">
-        <v>388196.06</v>
+        <v>1387184.07</v>
       </c>
       <c r="G91" t="n">
-        <v>19409.8</v>
+        <v>60899.65</v>
       </c>
       <c r="H91" t="n">
-        <v>368786.26</v>
+        <v>882753.5</v>
       </c>
       <c r="I91" t="n">
-        <v>258797.37</v>
+        <v>1326284.42</v>
       </c>
       <c r="J91" t="n">
-        <v>368786.26</v>
+        <v>1326284.42</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F92" t="n">
-        <v>63832.83</v>
+        <v>57649.21</v>
       </c>
       <c r="G92" t="n">
-        <v>5106.63</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>58726.21</v>
+        <v>36030.76</v>
       </c>
       <c r="I92" t="n">
-        <v>43209.92</v>
+        <v>57649.21</v>
       </c>
       <c r="J92" t="n">
-        <v>58726.21</v>
+        <v>57649.21</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E93" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F93" t="n">
-        <v>2111393.76</v>
+        <v>100886.11</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2657.44</v>
       </c>
       <c r="H93" t="n">
-        <v>2111393.76</v>
+        <v>68938.84</v>
       </c>
       <c r="I93" t="n">
-        <v>1394501.92</v>
+        <v>98228.67</v>
       </c>
       <c r="J93" t="n">
-        <v>2111393.76</v>
+        <v>98228.67</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E94" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F94" t="n">
-        <v>256486.68</v>
+        <v>100886.11</v>
       </c>
       <c r="G94" t="n">
-        <v>30778.4</v>
+        <v>1771.63</v>
       </c>
       <c r="H94" t="n">
-        <v>225708.28</v>
+        <v>68938.84</v>
       </c>
       <c r="I94" t="n">
-        <v>173301.81</v>
+        <v>99114.48</v>
       </c>
       <c r="J94" t="n">
-        <v>225708.28</v>
+        <v>99114.48</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,37 +4119,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E95" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F95" t="n">
-        <v>1334423.96</v>
+        <v>1678432.68</v>
       </c>
       <c r="G95" t="n">
-        <v>160130.88</v>
+        <v>44211.57</v>
       </c>
       <c r="H95" t="n">
-        <v>1174293.09</v>
+        <v>1108546.23</v>
       </c>
       <c r="I95" t="n">
-        <v>849178.89</v>
+        <v>1634221.11</v>
       </c>
       <c r="J95" t="n">
-        <v>1174293.09</v>
+        <v>1634221.11</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E96" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F96" t="n">
-        <v>170991.12</v>
+        <v>277436.81</v>
       </c>
       <c r="G96" t="n">
-        <v>8549.559999999999</v>
+        <v>7307.96</v>
       </c>
       <c r="H96" t="n">
-        <v>162441.57</v>
+        <v>184957.88</v>
       </c>
       <c r="I96" t="n">
-        <v>115534.54</v>
+        <v>270128.85</v>
       </c>
       <c r="J96" t="n">
-        <v>162441.57</v>
+        <v>270128.85</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E97" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F97" t="n">
-        <v>388196.06</v>
+        <v>1109747.26</v>
       </c>
       <c r="G97" t="n">
-        <v>46583.53</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>341612.53</v>
+        <v>706202.8</v>
       </c>
       <c r="I97" t="n">
-        <v>258797.37</v>
+        <v>1109747.26</v>
       </c>
       <c r="J97" t="n">
-        <v>341612.53</v>
+        <v>1109747.26</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,7 +4236,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4254,19 +4254,19 @@
         <v>21500</v>
       </c>
       <c r="F98" t="n">
-        <v>372598.9</v>
+        <v>387330.62</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>372598.9</v>
+        <v>255818.36</v>
       </c>
       <c r="I98" t="n">
-        <v>246088.57</v>
+        <v>387330.62</v>
       </c>
       <c r="J98" t="n">
-        <v>372598.9</v>
+        <v>387330.62</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,12 +4275,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
@@ -4290,22 +4290,22 @@
         <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="F99" t="n">
-        <v>154238.61</v>
+        <v>75664.59</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1993.08</v>
       </c>
       <c r="H99" t="n">
-        <v>154238.61</v>
+        <v>50443.06</v>
       </c>
       <c r="I99" t="n">
-        <v>102248.07</v>
+        <v>73671.50999999999</v>
       </c>
       <c r="J99" t="n">
-        <v>154238.61</v>
+        <v>73671.50999999999</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4326,25 +4326,25 @@
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
         <v>650</v>
       </c>
       <c r="F100" t="n">
-        <v>48813.34</v>
+        <v>19516.66</v>
       </c>
       <c r="G100" t="n">
-        <v>3905.07</v>
+        <v>856.8099999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>44908.28</v>
+        <v>13211.28</v>
       </c>
       <c r="I100" t="n">
-        <v>33042.88</v>
+        <v>18659.85</v>
       </c>
       <c r="J100" t="n">
-        <v>44908.28</v>
+        <v>18659.85</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,37 +4353,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>45858</v>
       </c>
       <c r="D101" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E101" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F101" t="n">
-        <v>1334423.96</v>
+        <v>85873.3</v>
       </c>
       <c r="G101" t="n">
-        <v>106753.92</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>1227670.05</v>
+        <v>58129.62</v>
       </c>
       <c r="I101" t="n">
-        <v>849178.89</v>
+        <v>85873.3</v>
       </c>
       <c r="J101" t="n">
-        <v>1227670.05</v>
+        <v>85873.3</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,37 +4392,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E102" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F102" t="n">
-        <v>55456.58</v>
+        <v>85873.3</v>
       </c>
       <c r="G102" t="n">
-        <v>6654.79</v>
+        <v>2261.99</v>
       </c>
       <c r="H102" t="n">
-        <v>48801.79</v>
+        <v>58129.62</v>
       </c>
       <c r="I102" t="n">
-        <v>34660.36</v>
+        <v>83611.31</v>
       </c>
       <c r="J102" t="n">
-        <v>48801.79</v>
+        <v>83611.31</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F103" t="n">
-        <v>97049.02</v>
+        <v>111094.83</v>
       </c>
       <c r="G103" t="n">
-        <v>4852.45</v>
+        <v>4877.25</v>
       </c>
       <c r="H103" t="n">
-        <v>92196.56</v>
+        <v>75064.07000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>66316.83</v>
+        <v>106217.58</v>
       </c>
       <c r="J103" t="n">
-        <v>92196.56</v>
+        <v>106217.58</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E104" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F104" t="n">
-        <v>97049.02</v>
+        <v>15613.33</v>
       </c>
       <c r="G104" t="n">
-        <v>2911.47</v>
+        <v>685.45</v>
       </c>
       <c r="H104" t="n">
-        <v>94137.55</v>
+        <v>10569.02</v>
       </c>
       <c r="I104" t="n">
-        <v>66316.83</v>
+        <v>14927.88</v>
       </c>
       <c r="J104" t="n">
-        <v>94137.55</v>
+        <v>14927.88</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,37 +4509,37 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F105" t="n">
-        <v>1614595.23</v>
+        <v>36030.76</v>
       </c>
       <c r="G105" t="n">
-        <v>80729.75999999999</v>
+        <v>949.09</v>
       </c>
       <c r="H105" t="n">
-        <v>1533865.47</v>
+        <v>24621.02</v>
       </c>
       <c r="I105" t="n">
-        <v>1066383.82</v>
+        <v>35081.67</v>
       </c>
       <c r="J105" t="n">
-        <v>1533865.47</v>
+        <v>35081.67</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4560,25 +4560,25 @@
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E106" t="n">
         <v>4200</v>
       </c>
       <c r="F106" t="n">
-        <v>266884.79</v>
+        <v>302658.34</v>
       </c>
       <c r="G106" t="n">
-        <v>13344.24</v>
+        <v>13287.2</v>
       </c>
       <c r="H106" t="n">
-        <v>253540.55</v>
+        <v>201772.23</v>
       </c>
       <c r="I106" t="n">
-        <v>177923.2</v>
+        <v>289371.14</v>
       </c>
       <c r="J106" t="n">
-        <v>253540.55</v>
+        <v>289371.14</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4592,32 +4592,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E107" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F107" t="n">
-        <v>1067539.17</v>
+        <v>630538.22</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>11072.66</v>
       </c>
       <c r="H107" t="n">
-        <v>1067539.17</v>
+        <v>420358.81</v>
       </c>
       <c r="I107" t="n">
-        <v>679343.11</v>
+        <v>619465.5600000001</v>
       </c>
       <c r="J107" t="n">
-        <v>1067539.17</v>
+        <v>619465.5600000001</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E108" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F108" t="n">
-        <v>372598.9</v>
+        <v>100886.11</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>4429.07</v>
       </c>
       <c r="H108" t="n">
-        <v>372598.9</v>
+        <v>68938.84</v>
       </c>
       <c r="I108" t="n">
-        <v>246088.57</v>
+        <v>96457.03999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>372598.9</v>
+        <v>96457.03999999999</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E109" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F109" t="n">
-        <v>72786.75999999999</v>
+        <v>222189.66</v>
       </c>
       <c r="G109" t="n">
-        <v>3639.34</v>
+        <v>3901.8</v>
       </c>
       <c r="H109" t="n">
-        <v>69147.42</v>
+        <v>150128.15</v>
       </c>
       <c r="I109" t="n">
-        <v>48524.51</v>
+        <v>218287.86</v>
       </c>
       <c r="J109" t="n">
-        <v>69147.42</v>
+        <v>218287.86</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E110" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F110" t="n">
-        <v>18774.36</v>
+        <v>481010.58</v>
       </c>
       <c r="G110" t="n">
-        <v>1501.95</v>
+        <v>8446.860000000001</v>
       </c>
       <c r="H110" t="n">
-        <v>17272.41</v>
+        <v>318872.18</v>
       </c>
       <c r="I110" t="n">
-        <v>12708.8</v>
+        <v>472563.72</v>
       </c>
       <c r="J110" t="n">
-        <v>17272.41</v>
+        <v>472563.72</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,7 +4743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4755,25 +4755,25 @@
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E111" t="n">
         <v>650</v>
       </c>
       <c r="F111" t="n">
-        <v>82607.2</v>
+        <v>46839.98</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>82607.2</v>
+        <v>31707.06</v>
       </c>
       <c r="I111" t="n">
-        <v>55918.72</v>
+        <v>46839.98</v>
       </c>
       <c r="J111" t="n">
-        <v>82607.2</v>
+        <v>46839.98</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E112" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F112" t="n">
-        <v>82607.2</v>
+        <v>1015466.78</v>
       </c>
       <c r="G112" t="n">
-        <v>4130.36</v>
+        <v>26748.39</v>
       </c>
       <c r="H112" t="n">
-        <v>78476.84</v>
+        <v>673174.61</v>
       </c>
       <c r="I112" t="n">
-        <v>55918.72</v>
+        <v>988718.39</v>
       </c>
       <c r="J112" t="n">
-        <v>78476.84</v>
+        <v>988718.39</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E113" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F113" t="n">
-        <v>106869.45</v>
+        <v>1282694.88</v>
       </c>
       <c r="G113" t="n">
-        <v>8549.559999999999</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>98319.89999999999</v>
+        <v>850325.8199999999</v>
       </c>
       <c r="I113" t="n">
-        <v>72209.09</v>
+        <v>1282694.88</v>
       </c>
       <c r="J113" t="n">
-        <v>98319.89999999999</v>
+        <v>1282694.88</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E114" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F114" t="n">
-        <v>15019.49</v>
+        <v>93679.96000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>1201.56</v>
+        <v>2467.62</v>
       </c>
       <c r="H114" t="n">
-        <v>13817.93</v>
+        <v>64014.64</v>
       </c>
       <c r="I114" t="n">
-        <v>10167.04</v>
+        <v>91212.34</v>
       </c>
       <c r="J114" t="n">
-        <v>13817.93</v>
+        <v>91212.34</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E115" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F115" t="n">
-        <v>34660.36</v>
+        <v>23419.99</v>
       </c>
       <c r="G115" t="n">
-        <v>4159.24</v>
+        <v>411.27</v>
       </c>
       <c r="H115" t="n">
-        <v>30501.12</v>
+        <v>15853.53</v>
       </c>
       <c r="I115" t="n">
-        <v>23684.58</v>
+        <v>23008.72</v>
       </c>
       <c r="J115" t="n">
-        <v>30501.12</v>
+        <v>23008.72</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E116" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F116" t="n">
-        <v>27728.29</v>
+        <v>97583.3</v>
       </c>
       <c r="G116" t="n">
-        <v>831.85</v>
+        <v>4284.07</v>
       </c>
       <c r="H116" t="n">
-        <v>26896.44</v>
+        <v>66056.38</v>
       </c>
       <c r="I116" t="n">
-        <v>18947.66</v>
+        <v>93299.23</v>
       </c>
       <c r="J116" t="n">
-        <v>26896.44</v>
+        <v>93299.23</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4977,37 +4977,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F117" t="n">
-        <v>15019.49</v>
+        <v>50443.06</v>
       </c>
       <c r="G117" t="n">
-        <v>450.58</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>14568.91</v>
+        <v>33628.7</v>
       </c>
       <c r="I117" t="n">
-        <v>10167.04</v>
+        <v>50443.06</v>
       </c>
       <c r="J117" t="n">
-        <v>14568.91</v>
+        <v>50443.06</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E118" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F118" t="n">
-        <v>97049.02</v>
+        <v>244408.62</v>
       </c>
       <c r="G118" t="n">
-        <v>7763.92</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>89285.09</v>
+        <v>165140.96</v>
       </c>
       <c r="I118" t="n">
-        <v>66316.83</v>
+        <v>244408.62</v>
       </c>
       <c r="J118" t="n">
-        <v>89285.09</v>
+        <v>244408.62</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E119" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F119" t="n">
-        <v>213738.9</v>
+        <v>2840424.53</v>
       </c>
       <c r="G119" t="n">
-        <v>25648.67</v>
+        <v>74819.57000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>188090.23</v>
+        <v>1876001.32</v>
       </c>
       <c r="I119" t="n">
-        <v>144418.18</v>
+        <v>2765604.96</v>
       </c>
       <c r="J119" t="n">
-        <v>188090.23</v>
+        <v>2765604.96</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E120" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F120" t="n">
-        <v>88961.60000000001</v>
+        <v>1807542.88</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>31741.64</v>
       </c>
       <c r="H120" t="n">
-        <v>88961.60000000001</v>
+        <v>1193819.02</v>
       </c>
       <c r="I120" t="n">
-        <v>56611.93</v>
+        <v>1775801.24</v>
       </c>
       <c r="J120" t="n">
-        <v>88961.60000000001</v>
+        <v>1775801.24</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E121" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F121" t="n">
-        <v>978577.5699999999</v>
+        <v>302658.34</v>
       </c>
       <c r="G121" t="n">
-        <v>29357.33</v>
+        <v>7972.32</v>
       </c>
       <c r="H121" t="n">
-        <v>949220.25</v>
+        <v>201772.23</v>
       </c>
       <c r="I121" t="n">
-        <v>622731.1800000001</v>
+        <v>294686.02</v>
       </c>
       <c r="J121" t="n">
-        <v>949220.25</v>
+        <v>294686.02</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,37 +5172,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E122" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F122" t="n">
-        <v>257064.36</v>
+        <v>2034536.64</v>
       </c>
       <c r="G122" t="n">
-        <v>20565.15</v>
+        <v>89319.49000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>236499.21</v>
+        <v>1294705.14</v>
       </c>
       <c r="I122" t="n">
-        <v>170413.45</v>
+        <v>1945217.15</v>
       </c>
       <c r="J122" t="n">
-        <v>236499.21</v>
+        <v>1945217.15</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5211,37 +5211,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F123" t="n">
-        <v>41592.44</v>
+        <v>184957.88</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>41592.44</v>
+        <v>117700.47</v>
       </c>
       <c r="I123" t="n">
-        <v>25995.27</v>
+        <v>184957.88</v>
       </c>
       <c r="J123" t="n">
-        <v>41592.44</v>
+        <v>184957.88</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5262,25 +5262,25 @@
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
         <v>1850</v>
       </c>
       <c r="F124" t="n">
-        <v>32060.84</v>
+        <v>11109.48</v>
       </c>
       <c r="G124" t="n">
-        <v>3847.3</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>28213.54</v>
+        <v>7506.41</v>
       </c>
       <c r="I124" t="n">
-        <v>21662.73</v>
+        <v>11109.48</v>
       </c>
       <c r="J124" t="n">
-        <v>28213.54</v>
+        <v>11109.48</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5301,25 +5301,25 @@
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E125" t="n">
         <v>1200</v>
       </c>
       <c r="F125" t="n">
-        <v>90116.94</v>
+        <v>180153.78</v>
       </c>
       <c r="G125" t="n">
-        <v>4505.85</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>85611.10000000001</v>
+        <v>123105.08</v>
       </c>
       <c r="I125" t="n">
-        <v>61579.91</v>
+        <v>180153.78</v>
       </c>
       <c r="J125" t="n">
-        <v>85611.10000000001</v>
+        <v>180153.78</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E126" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F126" t="n">
-        <v>22529.24</v>
+        <v>924789.38</v>
       </c>
       <c r="G126" t="n">
-        <v>675.88</v>
+        <v>16239.91</v>
       </c>
       <c r="H126" t="n">
-        <v>21853.36</v>
+        <v>588502.33</v>
       </c>
       <c r="I126" t="n">
-        <v>15250.56</v>
+        <v>908549.47</v>
       </c>
       <c r="J126" t="n">
-        <v>21853.36</v>
+        <v>908549.47</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E127" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F127" t="n">
-        <v>93871.82000000001</v>
+        <v>177751.73</v>
       </c>
       <c r="G127" t="n">
-        <v>7509.75</v>
+        <v>4682.16</v>
       </c>
       <c r="H127" t="n">
-        <v>86362.07000000001</v>
+        <v>120102.52</v>
       </c>
       <c r="I127" t="n">
-        <v>63544</v>
+        <v>173069.57</v>
       </c>
       <c r="J127" t="n">
-        <v>86362.07000000001</v>
+        <v>173069.57</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E128" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F128" t="n">
-        <v>48524.51</v>
+        <v>694793.0600000001</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>30502.55</v>
       </c>
       <c r="H128" t="n">
-        <v>48524.51</v>
+        <v>460593.15</v>
       </c>
       <c r="I128" t="n">
-        <v>32349.67</v>
+        <v>664290.51</v>
       </c>
       <c r="J128" t="n">
-        <v>48524.51</v>
+        <v>664290.51</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E129" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F129" t="n">
-        <v>235112.79</v>
+        <v>122504.57</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>5378.15</v>
       </c>
       <c r="H129" t="n">
-        <v>235112.79</v>
+        <v>83711.45</v>
       </c>
       <c r="I129" t="n">
-        <v>158860</v>
+        <v>117126.42</v>
       </c>
       <c r="J129" t="n">
-        <v>235112.79</v>
+        <v>117126.42</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E130" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F130" t="n">
-        <v>2732391.92</v>
+        <v>11710</v>
       </c>
       <c r="G130" t="n">
-        <v>136619.6</v>
+        <v>308.45</v>
       </c>
       <c r="H130" t="n">
-        <v>2595772.33</v>
+        <v>7926.77</v>
       </c>
       <c r="I130" t="n">
-        <v>1804649.55</v>
+        <v>11401.55</v>
       </c>
       <c r="J130" t="n">
-        <v>2595772.33</v>
+        <v>11401.55</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,12 +5523,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -5538,22 +5538,22 @@
         <v>14</v>
       </c>
       <c r="E131" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F131" t="n">
-        <v>1738794.86</v>
+        <v>155532.76</v>
       </c>
       <c r="G131" t="n">
-        <v>52163.85</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>1686631.01</v>
+        <v>105089.7</v>
       </c>
       <c r="I131" t="n">
-        <v>1148413.35</v>
+        <v>155532.76</v>
       </c>
       <c r="J131" t="n">
-        <v>1686631.01</v>
+        <v>155532.76</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,7 +5562,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5574,25 +5574,25 @@
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E132" t="n">
         <v>4200</v>
       </c>
       <c r="F132" t="n">
-        <v>291147.05</v>
+        <v>277436.81</v>
       </c>
       <c r="G132" t="n">
-        <v>14557.35</v>
+        <v>12179.93</v>
       </c>
       <c r="H132" t="n">
-        <v>276589.69</v>
+        <v>184957.88</v>
       </c>
       <c r="I132" t="n">
-        <v>194098.03</v>
+        <v>265256.88</v>
       </c>
       <c r="J132" t="n">
-        <v>276589.69</v>
+        <v>265256.88</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E133" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F133" t="n">
-        <v>1957155.15</v>
+        <v>331482.95</v>
       </c>
       <c r="G133" t="n">
-        <v>234858.62</v>
+        <v>8731.59</v>
       </c>
       <c r="H133" t="n">
-        <v>1722296.53</v>
+        <v>207176.84</v>
       </c>
       <c r="I133" t="n">
-        <v>1245462.37</v>
+        <v>322751.36</v>
       </c>
       <c r="J133" t="n">
-        <v>1722296.53</v>
+        <v>322751.36</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E134" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F134" t="n">
-        <v>2111393.76</v>
+        <v>327879.87</v>
       </c>
       <c r="G134" t="n">
-        <v>253367.25</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>1858026.51</v>
+        <v>218586.58</v>
       </c>
       <c r="I134" t="n">
-        <v>1394501.92</v>
+        <v>327879.87</v>
       </c>
       <c r="J134" t="n">
-        <v>1858026.51</v>
+        <v>327879.87</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E135" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F135" t="n">
-        <v>85495.56</v>
+        <v>1068912.4</v>
       </c>
       <c r="G135" t="n">
-        <v>4274.78</v>
+        <v>28156.2</v>
       </c>
       <c r="H135" t="n">
-        <v>81220.78</v>
+        <v>708604.85</v>
       </c>
       <c r="I135" t="n">
-        <v>57767.27</v>
+        <v>1040756.2</v>
       </c>
       <c r="J135" t="n">
-        <v>81220.78</v>
+        <v>1040756.2</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,37 +5718,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F136" t="n">
-        <v>10686.95</v>
+        <v>11710</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>308.45</v>
       </c>
       <c r="H136" t="n">
-        <v>10686.95</v>
+        <v>7926.77</v>
       </c>
       <c r="I136" t="n">
-        <v>7220.91</v>
+        <v>11401.55</v>
       </c>
       <c r="J136" t="n">
-        <v>10686.95</v>
+        <v>11401.55</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5757,37 +5757,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E137" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F137" t="n">
-        <v>173301.81</v>
+        <v>201772.23</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>5314.88</v>
       </c>
       <c r="H137" t="n">
-        <v>173301.81</v>
+        <v>134514.82</v>
       </c>
       <c r="I137" t="n">
-        <v>118422.91</v>
+        <v>196457.35</v>
       </c>
       <c r="J137" t="n">
-        <v>173301.81</v>
+        <v>196457.35</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5796,37 +5796,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E138" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F138" t="n">
-        <v>889615.98</v>
+        <v>245009.14</v>
       </c>
       <c r="G138" t="n">
-        <v>26688.48</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>862927.5</v>
+        <v>153130.71</v>
       </c>
       <c r="I138" t="n">
-        <v>566119.26</v>
+        <v>245009.14</v>
       </c>
       <c r="J138" t="n">
-        <v>862927.5</v>
+        <v>245009.14</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5835,37 +5835,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E139" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F139" t="n">
-        <v>170991.12</v>
+        <v>2219494.52</v>
       </c>
       <c r="G139" t="n">
-        <v>20518.93</v>
+        <v>38975.78</v>
       </c>
       <c r="H139" t="n">
-        <v>150472.19</v>
+        <v>1412405.6</v>
       </c>
       <c r="I139" t="n">
-        <v>115534.54</v>
+        <v>2180518.74</v>
       </c>
       <c r="J139" t="n">
-        <v>150472.19</v>
+        <v>2180518.74</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5874,37 +5874,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E140" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F140" t="n">
-        <v>257064.36</v>
+        <v>97583.3</v>
       </c>
       <c r="G140" t="n">
-        <v>12853.22</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>244211.14</v>
+        <v>66056.38</v>
       </c>
       <c r="I140" t="n">
-        <v>170413.45</v>
+        <v>97583.3</v>
       </c>
       <c r="J140" t="n">
-        <v>244211.14</v>
+        <v>97583.3</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5913,12 +5913,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -5928,22 +5928,22 @@
         <v>17</v>
       </c>
       <c r="E141" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F141" t="n">
-        <v>117845.23</v>
+        <v>428765.99</v>
       </c>
       <c r="G141" t="n">
-        <v>9427.620000000001</v>
+        <v>18823.53</v>
       </c>
       <c r="H141" t="n">
-        <v>108417.61</v>
+        <v>285843.99</v>
       </c>
       <c r="I141" t="n">
-        <v>80527.58</v>
+        <v>409942.46</v>
       </c>
       <c r="J141" t="n">
-        <v>108417.61</v>
+        <v>409942.46</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5964,25 +5964,25 @@
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E142" t="n">
         <v>650</v>
       </c>
       <c r="F142" t="n">
-        <v>11264.62</v>
+        <v>46839.98</v>
       </c>
       <c r="G142" t="n">
-        <v>563.23</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>10701.39</v>
+        <v>31707.06</v>
       </c>
       <c r="I142" t="n">
-        <v>7625.28</v>
+        <v>46839.98</v>
       </c>
       <c r="J142" t="n">
-        <v>10701.39</v>
+        <v>46839.98</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5991,37 +5991,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="D143" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E143" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F143" t="n">
-        <v>149617.23</v>
+        <v>126107.64</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>2214.53</v>
       </c>
       <c r="H143" t="n">
-        <v>149617.23</v>
+        <v>84071.75999999999</v>
       </c>
       <c r="I143" t="n">
-        <v>101092.72</v>
+        <v>123893.11</v>
       </c>
       <c r="J143" t="n">
-        <v>149617.23</v>
+        <v>123893.11</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6030,37 +6030,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E144" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F144" t="n">
-        <v>266884.79</v>
+        <v>1068912.4</v>
       </c>
       <c r="G144" t="n">
-        <v>21350.78</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>245534.01</v>
+        <v>708604.85</v>
       </c>
       <c r="I144" t="n">
-        <v>177923.2</v>
+        <v>1068912.4</v>
       </c>
       <c r="J144" t="n">
-        <v>245534.01</v>
+        <v>1068912.4</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6069,37 +6069,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E145" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F145" t="n">
-        <v>318875.34</v>
+        <v>151329.17</v>
       </c>
       <c r="G145" t="n">
-        <v>38265.04</v>
+        <v>3986.16</v>
       </c>
       <c r="H145" t="n">
-        <v>280610.3</v>
+        <v>100886.11</v>
       </c>
       <c r="I145" t="n">
-        <v>199297.09</v>
+        <v>147343.01</v>
       </c>
       <c r="J145" t="n">
-        <v>280610.3</v>
+        <v>147343.01</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6108,37 +6108,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E146" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F146" t="n">
-        <v>355846.39</v>
+        <v>2840424.53</v>
       </c>
       <c r="G146" t="n">
-        <v>17792.32</v>
+        <v>124699.29</v>
       </c>
       <c r="H146" t="n">
-        <v>338054.07</v>
+        <v>1876001.32</v>
       </c>
       <c r="I146" t="n">
-        <v>226447.7</v>
+        <v>2715725.24</v>
       </c>
       <c r="J146" t="n">
-        <v>338054.07</v>
+        <v>2715725.24</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6159,25 +6159,25 @@
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E147" t="n">
         <v>650</v>
       </c>
       <c r="F147" t="n">
-        <v>22529.24</v>
+        <v>81969.97</v>
       </c>
       <c r="G147" t="n">
-        <v>1802.34</v>
+        <v>1439.45</v>
       </c>
       <c r="H147" t="n">
-        <v>20726.9</v>
+        <v>55487.36</v>
       </c>
       <c r="I147" t="n">
-        <v>15250.56</v>
+        <v>80530.52</v>
       </c>
       <c r="J147" t="n">
-        <v>20726.9</v>
+        <v>80530.52</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6186,12 +6186,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
@@ -6201,22 +6201,22 @@
         <v>3</v>
       </c>
       <c r="E148" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F148" t="n">
-        <v>11264.62</v>
+        <v>387330.62</v>
       </c>
       <c r="G148" t="n">
-        <v>563.23</v>
+        <v>10202.67</v>
       </c>
       <c r="H148" t="n">
-        <v>10701.39</v>
+        <v>255818.36</v>
       </c>
       <c r="I148" t="n">
-        <v>7625.28</v>
+        <v>377127.95</v>
       </c>
       <c r="J148" t="n">
-        <v>10701.39</v>
+        <v>377127.95</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -6225,37 +6225,37 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E149" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F149" t="n">
-        <v>194098.03</v>
+        <v>832310.4399999999</v>
       </c>
       <c r="G149" t="n">
-        <v>9704.9</v>
+        <v>36539.79</v>
       </c>
       <c r="H149" t="n">
-        <v>184393.13</v>
+        <v>529652.1</v>
       </c>
       <c r="I149" t="n">
-        <v>129398.69</v>
+        <v>795770.65</v>
       </c>
       <c r="J149" t="n">
-        <v>184393.13</v>
+        <v>795770.65</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -6264,12 +6264,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
@@ -6279,22 +6279,22 @@
         <v>17</v>
       </c>
       <c r="E150" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F150" t="n">
-        <v>235690.47</v>
+        <v>66356.64</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>235690.47</v>
+        <v>44918.34</v>
       </c>
       <c r="I150" t="n">
-        <v>147306.54</v>
+        <v>66356.64</v>
       </c>
       <c r="J150" t="n">
-        <v>235690.47</v>
+        <v>66356.64</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -6303,37 +6303,37 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E151" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F151" t="n">
-        <v>2135078.34</v>
+        <v>1936653.09</v>
       </c>
       <c r="G151" t="n">
-        <v>64052.35</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>2071025.99</v>
+        <v>1279091.81</v>
       </c>
       <c r="I151" t="n">
-        <v>1358686.22</v>
+        <v>1936653.09</v>
       </c>
       <c r="J151" t="n">
-        <v>2071025.99</v>
+        <v>1936653.09</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6354,25 +6354,25 @@
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E152" t="n">
         <v>650</v>
       </c>
       <c r="F152" t="n">
-        <v>93871.82000000001</v>
+        <v>39033.32</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>93871.82000000001</v>
+        <v>26422.55</v>
       </c>
       <c r="I152" t="n">
-        <v>63544</v>
+        <v>39033.32</v>
       </c>
       <c r="J152" t="n">
-        <v>93871.82000000001</v>
+        <v>39033.32</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6393,25 +6393,25 @@
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E153" t="n">
         <v>4200</v>
       </c>
       <c r="F153" t="n">
-        <v>412458.32</v>
+        <v>504430.57</v>
       </c>
       <c r="G153" t="n">
-        <v>32996.67</v>
+        <v>22145.33</v>
       </c>
       <c r="H153" t="n">
-        <v>379461.65</v>
+        <v>336287.05</v>
       </c>
       <c r="I153" t="n">
-        <v>274972.21</v>
+        <v>482285.24</v>
       </c>
       <c r="J153" t="n">
-        <v>379461.65</v>
+        <v>482285.24</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -6420,85 +6420,85 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E154" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F154" t="n">
-        <v>45058.47</v>
+        <v>216184.53</v>
       </c>
       <c r="G154" t="n">
-        <v>5407.02</v>
+        <v>9490.860000000001</v>
       </c>
       <c r="H154" t="n">
-        <v>39651.45</v>
+        <v>135115.33</v>
       </c>
       <c r="I154" t="n">
-        <v>30501.12</v>
+        <v>206693.67</v>
       </c>
       <c r="J154" t="n">
-        <v>19825.73</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>19825.73</v>
+        <v>206693.67</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E155" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F155" t="n">
-        <v>411302.97</v>
+        <v>166642.24</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>7315.87</v>
       </c>
       <c r="H155" t="n">
-        <v>411302.97</v>
+        <v>112596.11</v>
       </c>
       <c r="I155" t="n">
-        <v>272661.52</v>
+        <v>159326.37</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>79663.17999999999</v>
       </c>
       <c r="K155" t="n">
-        <v>411302.97</v>
+        <v>79663.19</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6510,496 +6510,496 @@
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E156" t="n">
         <v>1200</v>
       </c>
       <c r="F156" t="n">
-        <v>41592.44</v>
+        <v>79267.66</v>
       </c>
       <c r="G156" t="n">
-        <v>3327.39</v>
+        <v>3479.98</v>
       </c>
       <c r="H156" t="n">
-        <v>38265.04</v>
+        <v>54166.24</v>
       </c>
       <c r="I156" t="n">
-        <v>28421.5</v>
+        <v>75787.67999999999</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>38265.04</v>
+        <v>75787.67999999999</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E157" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F157" t="n">
-        <v>145573.52</v>
+        <v>106891.24</v>
       </c>
       <c r="G157" t="n">
-        <v>17468.82</v>
+        <v>2815.62</v>
       </c>
       <c r="H157" t="n">
-        <v>128104.7</v>
+        <v>70860.49000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>97049.02</v>
+        <v>104075.62</v>
       </c>
       <c r="J157" t="n">
-        <v>38431.41</v>
+        <v>31222.69</v>
       </c>
       <c r="K157" t="n">
-        <v>89673.28999999999</v>
+        <v>72852.92999999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E158" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F158" t="n">
-        <v>2732391.92</v>
+        <v>89776.63</v>
       </c>
       <c r="G158" t="n">
-        <v>218591.35</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>2513800.57</v>
+        <v>60771.87</v>
       </c>
       <c r="I158" t="n">
-        <v>1804649.55</v>
+        <v>89776.63</v>
       </c>
       <c r="J158" t="n">
-        <v>1256900.28</v>
+        <v>26932.99</v>
       </c>
       <c r="K158" t="n">
-        <v>1256900.28</v>
+        <v>62843.64</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F159" t="n">
-        <v>78852.33</v>
+        <v>106891.24</v>
       </c>
       <c r="G159" t="n">
-        <v>2365.57</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>76486.75999999999</v>
+        <v>70860.49000000001</v>
       </c>
       <c r="I159" t="n">
-        <v>53376.96</v>
+        <v>106891.24</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>76486.75999999999</v>
+        <v>106891.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E160" t="n">
-        <v>4200</v>
+        <v>21500</v>
       </c>
       <c r="F160" t="n">
-        <v>388196.06</v>
+        <v>1936653.09</v>
       </c>
       <c r="G160" t="n">
-        <v>19409.8</v>
+        <v>85022.24000000001</v>
       </c>
       <c r="H160" t="n">
-        <v>368786.26</v>
+        <v>1279091.81</v>
       </c>
       <c r="I160" t="n">
-        <v>258797.37</v>
+        <v>1851630.85</v>
       </c>
       <c r="J160" t="n">
-        <v>184393.13</v>
+        <v>555489.26</v>
       </c>
       <c r="K160" t="n">
-        <v>184393.13</v>
+        <v>1296141.59</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E161" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F161" t="n">
-        <v>1690270.35</v>
+        <v>641347.4399999999</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>11262.48</v>
       </c>
       <c r="H161" t="n">
-        <v>1690270.35</v>
+        <v>425162.91</v>
       </c>
       <c r="I161" t="n">
-        <v>1075626.59</v>
+        <v>630084.96</v>
       </c>
       <c r="J161" t="n">
-        <v>507081.11</v>
+        <v>315042.48</v>
       </c>
       <c r="K161" t="n">
-        <v>1183189.25</v>
+        <v>315042.48</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E162" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F162" t="n">
-        <v>242622.54</v>
+        <v>1202226.2</v>
       </c>
       <c r="G162" t="n">
-        <v>12131.13</v>
+        <v>31667.82</v>
       </c>
       <c r="H162" t="n">
-        <v>230491.41</v>
+        <v>765053.03</v>
       </c>
       <c r="I162" t="n">
-        <v>161748.36</v>
+        <v>1170558.38</v>
       </c>
       <c r="J162" t="n">
-        <v>69147.42</v>
+        <v>585279.1899999999</v>
       </c>
       <c r="K162" t="n">
-        <v>161343.99</v>
+        <v>585279.1899999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E163" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F163" t="n">
-        <v>128243.34</v>
+        <v>85873.3</v>
       </c>
       <c r="G163" t="n">
-        <v>3847.3</v>
+        <v>3769.98</v>
       </c>
       <c r="H163" t="n">
-        <v>124396.04</v>
+        <v>58129.62</v>
       </c>
       <c r="I163" t="n">
-        <v>86650.91</v>
+        <v>82103.32000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>24631</v>
       </c>
       <c r="K163" t="n">
-        <v>124396.04</v>
+        <v>57472.32</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E164" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F164" t="n">
-        <v>485245.08</v>
+        <v>11710</v>
       </c>
       <c r="G164" t="n">
-        <v>38819.61</v>
+        <v>205.64</v>
       </c>
       <c r="H164" t="n">
-        <v>446425.47</v>
+        <v>7926.77</v>
       </c>
       <c r="I164" t="n">
-        <v>323496.72</v>
+        <v>11504.36</v>
       </c>
       <c r="J164" t="n">
-        <v>223212.74</v>
+        <v>3451.31</v>
       </c>
       <c r="K164" t="n">
-        <v>223212.74</v>
+        <v>8053.05</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E165" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F165" t="n">
-        <v>2359793.02</v>
+        <v>144123.02</v>
       </c>
       <c r="G165" t="n">
-        <v>188783.44</v>
+        <v>2530.89</v>
       </c>
       <c r="H165" t="n">
-        <v>2171009.58</v>
+        <v>90076.89</v>
       </c>
       <c r="I165" t="n">
-        <v>1558560.97</v>
+        <v>141592.13</v>
       </c>
       <c r="J165" t="n">
-        <v>1085504.79</v>
+        <v>42477.64</v>
       </c>
       <c r="K165" t="n">
-        <v>1085504.79</v>
+        <v>99114.49000000001</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E166" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F166" t="n">
-        <v>160304.18</v>
+        <v>587901.8199999999</v>
       </c>
       <c r="G166" t="n">
-        <v>12824.33</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>147479.84</v>
+        <v>389732.67</v>
       </c>
       <c r="I166" t="n">
-        <v>108313.63</v>
+        <v>587901.8199999999</v>
       </c>
       <c r="J166" t="n">
-        <v>73739.92</v>
+        <v>176370.55</v>
       </c>
       <c r="K166" t="n">
-        <v>73739.92</v>
+        <v>411531.27</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E167" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F167" t="n">
-        <v>75097.45</v>
+        <v>641347.4399999999</v>
       </c>
       <c r="G167" t="n">
-        <v>3754.87</v>
+        <v>11262.48</v>
       </c>
       <c r="H167" t="n">
-        <v>71342.58</v>
+        <v>425162.91</v>
       </c>
       <c r="I167" t="n">
-        <v>50835.2</v>
+        <v>630084.96</v>
       </c>
       <c r="J167" t="n">
-        <v>35671.29</v>
+        <v>315042.48</v>
       </c>
       <c r="K167" t="n">
-        <v>35671.29</v>
+        <v>315042.48</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E168" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F168" t="n">
-        <v>160304.18</v>
+        <v>72061.50999999999</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>3163.62</v>
       </c>
       <c r="H168" t="n">
-        <v>160304.18</v>
+        <v>45038.44</v>
       </c>
       <c r="I168" t="n">
-        <v>108313.63</v>
+        <v>68897.89</v>
       </c>
       <c r="J168" t="n">
-        <v>48091.25</v>
+        <v>34448.94</v>
       </c>
       <c r="K168" t="n">
-        <v>112212.92</v>
+        <v>34448.95</v>
       </c>
     </row>
     <row r="169">
@@ -7017,229 +7017,229 @@
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E169" t="n">
         <v>4200</v>
       </c>
       <c r="F169" t="n">
-        <v>412458.32</v>
+        <v>252215.29</v>
       </c>
       <c r="G169" t="n">
-        <v>49495</v>
+        <v>11072.66</v>
       </c>
       <c r="H169" t="n">
-        <v>362963.32</v>
+        <v>168143.52</v>
       </c>
       <c r="I169" t="n">
-        <v>274972.21</v>
+        <v>241142.63</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>72342.78999999999</v>
       </c>
       <c r="K169" t="n">
-        <v>362963.32</v>
+        <v>168799.84</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E170" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F170" t="n">
-        <v>159437.67</v>
+        <v>19516.66</v>
       </c>
       <c r="G170" t="n">
-        <v>7971.88</v>
+        <v>856.8099999999999</v>
       </c>
       <c r="H170" t="n">
-        <v>151465.78</v>
+        <v>13211.28</v>
       </c>
       <c r="I170" t="n">
-        <v>108949.07</v>
+        <v>18659.85</v>
       </c>
       <c r="J170" t="n">
-        <v>45439.74</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>106026.05</v>
+        <v>18659.85</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E171" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F171" t="n">
-        <v>616954.46</v>
+        <v>245009.14</v>
       </c>
       <c r="G171" t="n">
-        <v>18508.63</v>
+        <v>4302.52</v>
       </c>
       <c r="H171" t="n">
-        <v>598445.8199999999</v>
+        <v>153130.71</v>
       </c>
       <c r="I171" t="n">
-        <v>408992.28</v>
+        <v>240706.62</v>
       </c>
       <c r="J171" t="n">
-        <v>179533.75</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>418912.08</v>
+        <v>240706.62</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E172" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F172" t="n">
-        <v>346603.63</v>
+        <v>39033.32</v>
       </c>
       <c r="G172" t="n">
-        <v>10398.11</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>336205.52</v>
+        <v>26422.55</v>
       </c>
       <c r="I172" t="n">
-        <v>216627.27</v>
+        <v>39033.32</v>
       </c>
       <c r="J172" t="n">
-        <v>168102.76</v>
+        <v>19516.66</v>
       </c>
       <c r="K172" t="n">
-        <v>168102.76</v>
+        <v>19516.66</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D173" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E173" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F173" t="n">
-        <v>224425.85</v>
+        <v>97583.3</v>
       </c>
       <c r="G173" t="n">
-        <v>26931.1</v>
+        <v>2570.44</v>
       </c>
       <c r="H173" t="n">
-        <v>197494.75</v>
+        <v>66056.38</v>
       </c>
       <c r="I173" t="n">
-        <v>151639.09</v>
+        <v>95012.86</v>
       </c>
       <c r="J173" t="n">
-        <v>59248.42</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>138246.32</v>
+        <v>95012.86</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E174" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F174" t="n">
-        <v>15019.49</v>
+        <v>36030.76</v>
       </c>
       <c r="G174" t="n">
-        <v>1201.56</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>13817.93</v>
+        <v>24621.02</v>
       </c>
       <c r="I174" t="n">
-        <v>10167.04</v>
+        <v>36030.76</v>
       </c>
       <c r="J174" t="n">
-        <v>6908.97</v>
+        <v>10809.23</v>
       </c>
       <c r="K174" t="n">
-        <v>6908.97</v>
+        <v>25221.53</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7251,73 +7251,73 @@
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E175" t="n">
         <v>15400</v>
       </c>
       <c r="F175" t="n">
-        <v>800654.38</v>
+        <v>369915.75</v>
       </c>
       <c r="G175" t="n">
-        <v>96078.53</v>
+        <v>16239.91</v>
       </c>
       <c r="H175" t="n">
-        <v>704575.85</v>
+        <v>235400.93</v>
       </c>
       <c r="I175" t="n">
-        <v>509507.33</v>
+        <v>353675.84</v>
       </c>
       <c r="J175" t="n">
-        <v>352287.93</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>352287.93</v>
+        <v>353675.84</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E176" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F176" t="n">
-        <v>565541.58</v>
+        <v>244408.62</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>4291.98</v>
       </c>
       <c r="H176" t="n">
-        <v>565541.58</v>
+        <v>165140.96</v>
       </c>
       <c r="I176" t="n">
-        <v>374909.59</v>
+        <v>240116.64</v>
       </c>
       <c r="J176" t="n">
-        <v>282770.79</v>
+        <v>120058.32</v>
       </c>
       <c r="K176" t="n">
-        <v>282770.79</v>
+        <v>120058.32</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7329,184 +7329,184 @@
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E177" t="n">
         <v>8900</v>
       </c>
       <c r="F177" t="n">
-        <v>616954.46</v>
+        <v>1068912.4</v>
       </c>
       <c r="G177" t="n">
-        <v>18508.63</v>
+        <v>28156.2</v>
       </c>
       <c r="H177" t="n">
-        <v>598445.8199999999</v>
+        <v>708604.85</v>
       </c>
       <c r="I177" t="n">
-        <v>408992.28</v>
+        <v>1040756.2</v>
       </c>
       <c r="J177" t="n">
-        <v>299222.91</v>
+        <v>312226.86</v>
       </c>
       <c r="K177" t="n">
-        <v>299222.91</v>
+        <v>728529.34</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E178" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F178" t="n">
-        <v>69320.73</v>
+        <v>320673.72</v>
       </c>
       <c r="G178" t="n">
-        <v>5545.66</v>
+        <v>14078.1</v>
       </c>
       <c r="H178" t="n">
-        <v>63775.07</v>
+        <v>212581.46</v>
       </c>
       <c r="I178" t="n">
-        <v>43325.45</v>
+        <v>306595.62</v>
       </c>
       <c r="J178" t="n">
-        <v>31887.53</v>
+        <v>91978.69</v>
       </c>
       <c r="K178" t="n">
-        <v>31887.53</v>
+        <v>214616.93</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E179" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F179" t="n">
-        <v>1601308.76</v>
+        <v>1282694.88</v>
       </c>
       <c r="G179" t="n">
-        <v>80065.44</v>
+        <v>33787.44</v>
       </c>
       <c r="H179" t="n">
-        <v>1521243.32</v>
+        <v>850325.8199999999</v>
       </c>
       <c r="I179" t="n">
-        <v>1019014.66</v>
+        <v>1248907.44</v>
       </c>
       <c r="J179" t="n">
-        <v>760621.66</v>
+        <v>624453.72</v>
       </c>
       <c r="K179" t="n">
-        <v>760621.66</v>
+        <v>624453.72</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E180" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F180" t="n">
-        <v>18774.36</v>
+        <v>172947.62</v>
       </c>
       <c r="G180" t="n">
-        <v>2252.92</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>16521.44</v>
+        <v>108092.27</v>
       </c>
       <c r="I180" t="n">
-        <v>12708.8</v>
+        <v>172947.62</v>
       </c>
       <c r="J180" t="n">
-        <v>8260.719999999999</v>
+        <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>8260.719999999999</v>
+        <v>172947.62</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E181" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F181" t="n">
-        <v>509507.33</v>
+        <v>2311973.46</v>
       </c>
       <c r="G181" t="n">
-        <v>61140.88</v>
+        <v>60899.65</v>
       </c>
       <c r="H181" t="n">
-        <v>448366.45</v>
+        <v>1471255.84</v>
       </c>
       <c r="I181" t="n">
-        <v>339671.55</v>
+        <v>2251073.81</v>
       </c>
       <c r="J181" t="n">
-        <v>134509.94</v>
+        <v>1125536.91</v>
       </c>
       <c r="K181" t="n">
-        <v>313856.52</v>
+        <v>1125536.9</v>
       </c>
     </row>
   </sheetData>

--- a/demo_data/sectors/toptan_ticaret/sales_ledger.xlsx
+++ b/demo_data/sectors/toptan_ticaret/sales_ledger.xlsx
@@ -492,37 +492,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>2400</v>
+        <v>420</v>
       </c>
       <c r="F2" t="n">
-        <v>158535.33</v>
+        <v>136295.75</v>
       </c>
       <c r="G2" t="n">
-        <v>6959.94</v>
+        <v>0.03</v>
       </c>
       <c r="H2" t="n">
-        <v>99084.58</v>
+        <v>113579.81</v>
       </c>
       <c r="I2" t="n">
-        <v>151575.39</v>
+        <v>136295.72</v>
       </c>
       <c r="J2" t="n">
-        <v>151575.39</v>
+        <v>136295.72</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -531,37 +531,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>1850</v>
+        <v>980</v>
       </c>
       <c r="F3" t="n">
-        <v>111094.83</v>
+        <v>671382.88</v>
       </c>
       <c r="G3" t="n">
-        <v>1950.9</v>
+        <v>37816.2</v>
       </c>
       <c r="H3" t="n">
-        <v>75064.07000000001</v>
+        <v>575471.04</v>
       </c>
       <c r="I3" t="n">
-        <v>109143.93</v>
+        <v>633566.6800000001</v>
       </c>
       <c r="J3" t="n">
-        <v>109143.93</v>
+        <v>633566.6800000001</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,37 +570,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>45662</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>21500</v>
+        <v>3600</v>
       </c>
       <c r="F4" t="n">
-        <v>645551.03</v>
+        <v>1168249.48</v>
       </c>
       <c r="G4" t="n">
-        <v>17004.45</v>
+        <v>65802.63</v>
       </c>
       <c r="H4" t="n">
-        <v>426363.94</v>
+        <v>1005992.61</v>
       </c>
       <c r="I4" t="n">
-        <v>628546.58</v>
+        <v>1102446.85</v>
       </c>
       <c r="J4" t="n">
-        <v>628546.58</v>
+        <v>1102446.85</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,37 +609,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>21500</v>
+        <v>3600</v>
       </c>
       <c r="F5" t="n">
-        <v>1549322.47</v>
+        <v>778832.99</v>
       </c>
       <c r="G5" t="n">
-        <v>27207.12</v>
+        <v>26321.05</v>
       </c>
       <c r="H5" t="n">
-        <v>1023273.45</v>
+        <v>670661.74</v>
       </c>
       <c r="I5" t="n">
-        <v>1522115.35</v>
+        <v>752511.9399999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1522115.35</v>
+        <v>752511.9399999999</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,37 +648,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F6" t="n">
-        <v>216184.53</v>
+        <v>400233.62</v>
       </c>
       <c r="G6" t="n">
-        <v>3796.34</v>
+        <v>22543.49</v>
       </c>
       <c r="H6" t="n">
-        <v>135115.33</v>
+        <v>346147.99</v>
       </c>
       <c r="I6" t="n">
-        <v>212388.19</v>
+        <v>377690.13</v>
       </c>
       <c r="J6" t="n">
-        <v>212388.19</v>
+        <v>377690.13</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>1200</v>
+        <v>280</v>
       </c>
       <c r="F7" t="n">
-        <v>165741.47</v>
+        <v>161535.73</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>113256.67</v>
+        <v>135574.63</v>
       </c>
       <c r="I7" t="n">
-        <v>165741.47</v>
+        <v>161535.73</v>
       </c>
       <c r="J7" t="n">
-        <v>165741.47</v>
+        <v>161535.73</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,37 +726,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F8" t="n">
-        <v>115298.42</v>
+        <v>933878.4399999999</v>
       </c>
       <c r="G8" t="n">
-        <v>3037.07</v>
+        <v>21040.59</v>
       </c>
       <c r="H8" t="n">
-        <v>72061.50999999999</v>
+        <v>807678.65</v>
       </c>
       <c r="I8" t="n">
-        <v>112261.35</v>
+        <v>912837.85</v>
       </c>
       <c r="J8" t="n">
-        <v>112261.35</v>
+        <v>912837.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,37 +765,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="F9" t="n">
-        <v>93679.96000000001</v>
+        <v>40383.93</v>
       </c>
       <c r="G9" t="n">
-        <v>2467.62</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>63414.13</v>
+        <v>33893.66</v>
       </c>
       <c r="I9" t="n">
-        <v>91212.34</v>
+        <v>40383.93</v>
       </c>
       <c r="J9" t="n">
-        <v>91212.34</v>
+        <v>40383.93</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,37 +804,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>2400</v>
+        <v>580</v>
       </c>
       <c r="F10" t="n">
-        <v>187359.93</v>
+        <v>334609.73</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>7538.87</v>
       </c>
       <c r="H10" t="n">
-        <v>117099.95</v>
+        <v>276918.4</v>
       </c>
       <c r="I10" t="n">
-        <v>187359.93</v>
+        <v>327070.86</v>
       </c>
       <c r="J10" t="n">
-        <v>187359.93</v>
+        <v>327070.86</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>1850</v>
+        <v>3600</v>
       </c>
       <c r="F11" t="n">
-        <v>55547.41</v>
+        <v>2336498.96</v>
       </c>
       <c r="G11" t="n">
-        <v>2438.62</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>37532.04</v>
+        <v>2011985.21</v>
       </c>
       <c r="I11" t="n">
-        <v>53108.79</v>
+        <v>2336498.96</v>
       </c>
       <c r="J11" t="n">
-        <v>53108.79</v>
+        <v>2336498.96</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -882,37 +882,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="F12" t="n">
-        <v>15613.33</v>
+        <v>456122.1</v>
       </c>
       <c r="G12" t="n">
-        <v>411.27</v>
+        <v>10276.58</v>
       </c>
       <c r="H12" t="n">
-        <v>10569.02</v>
+        <v>388695.35</v>
       </c>
       <c r="I12" t="n">
-        <v>15202.06</v>
+        <v>445845.52</v>
       </c>
       <c r="J12" t="n">
-        <v>15202.06</v>
+        <v>445845.52</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -921,37 +921,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>21500</v>
+        <v>1150</v>
       </c>
       <c r="F13" t="n">
-        <v>129110.21</v>
+        <v>539053.39</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>30362.63</v>
       </c>
       <c r="H13" t="n">
-        <v>85272.78999999999</v>
+        <v>459367.23</v>
       </c>
       <c r="I13" t="n">
-        <v>129110.21</v>
+        <v>508690.76</v>
       </c>
       <c r="J13" t="n">
-        <v>129110.21</v>
+        <v>508690.76</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,37 +960,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>8900</v>
+        <v>280</v>
       </c>
       <c r="F14" t="n">
-        <v>160336.86</v>
+        <v>181727.7</v>
       </c>
       <c r="G14" t="n">
-        <v>4223.43</v>
+        <v>6141.58</v>
       </c>
       <c r="H14" t="n">
-        <v>106290.73</v>
+        <v>152521.46</v>
       </c>
       <c r="I14" t="n">
-        <v>156113.43</v>
+        <v>175586.12</v>
       </c>
       <c r="J14" t="n">
-        <v>156113.43</v>
+        <v>175586.12</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>15400</v>
+        <v>1150</v>
       </c>
       <c r="F15" t="n">
-        <v>1017268.32</v>
+        <v>290259.52</v>
       </c>
       <c r="G15" t="n">
-        <v>44659.75</v>
+        <v>16349.11</v>
       </c>
       <c r="H15" t="n">
-        <v>647352.5699999999</v>
+        <v>247351.59</v>
       </c>
       <c r="I15" t="n">
-        <v>972608.5699999999</v>
+        <v>273910.41</v>
       </c>
       <c r="J15" t="n">
-        <v>972608.5699999999</v>
+        <v>273910.41</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>2400</v>
+        <v>420</v>
       </c>
       <c r="F16" t="n">
-        <v>302658.34</v>
+        <v>242303.6</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>8188.77</v>
       </c>
       <c r="H16" t="n">
-        <v>189161.46</v>
+        <v>201919.66</v>
       </c>
       <c r="I16" t="n">
-        <v>302658.34</v>
+        <v>234114.83</v>
       </c>
       <c r="J16" t="n">
-        <v>302658.34</v>
+        <v>234114.83</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>650</v>
+        <v>980</v>
       </c>
       <c r="F17" t="n">
-        <v>85873.3</v>
+        <v>318023.47</v>
       </c>
       <c r="G17" t="n">
-        <v>3769.98</v>
+        <v>17912.94</v>
       </c>
       <c r="H17" t="n">
-        <v>58129.62</v>
+        <v>272591.55</v>
       </c>
       <c r="I17" t="n">
-        <v>82103.32000000001</v>
+        <v>300110.53</v>
       </c>
       <c r="J17" t="n">
-        <v>82103.32000000001</v>
+        <v>300110.53</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F18" t="n">
-        <v>81969.97</v>
+        <v>1000584.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2159.17</v>
+        <v>33815.24</v>
       </c>
       <c r="H18" t="n">
-        <v>55487.36</v>
+        <v>865369.98</v>
       </c>
       <c r="I18" t="n">
-        <v>79810.8</v>
+        <v>966768.8</v>
       </c>
       <c r="J18" t="n">
-        <v>79810.8</v>
+        <v>966768.8</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,12 +1155,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1170,22 +1170,22 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1850</v>
+        <v>1150</v>
       </c>
       <c r="F19" t="n">
-        <v>222189.66</v>
+        <v>829312.9</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>150128.15</v>
+        <v>706718.8199999999</v>
       </c>
       <c r="I19" t="n">
-        <v>222189.66</v>
+        <v>829312.9</v>
       </c>
       <c r="J19" t="n">
-        <v>222189.66</v>
+        <v>829312.9</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F20" t="n">
-        <v>739831.51</v>
+        <v>1200700.85</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>470801.87</v>
+        <v>1038443.98</v>
       </c>
       <c r="I20" t="n">
-        <v>739831.51</v>
+        <v>1200700.85</v>
       </c>
       <c r="J20" t="n">
-        <v>739831.51</v>
+        <v>1200700.85</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,37 +1233,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>4200</v>
+        <v>1150</v>
       </c>
       <c r="F21" t="n">
-        <v>630538.22</v>
+        <v>331725.16</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>420358.81</v>
+        <v>282687.53</v>
       </c>
       <c r="I21" t="n">
-        <v>630538.22</v>
+        <v>331725.16</v>
       </c>
       <c r="J21" t="n">
-        <v>630538.22</v>
+        <v>331725.16</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>8900</v>
+        <v>1150</v>
       </c>
       <c r="F22" t="n">
-        <v>1229249.26</v>
+        <v>207328.23</v>
       </c>
       <c r="G22" t="n">
-        <v>21586.42</v>
+        <v>7006.76</v>
       </c>
       <c r="H22" t="n">
-        <v>814895.58</v>
+        <v>176679.71</v>
       </c>
       <c r="I22" t="n">
-        <v>1207662.84</v>
+        <v>200321.47</v>
       </c>
       <c r="J22" t="n">
-        <v>1207662.84</v>
+        <v>200321.47</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>1850</v>
+        <v>420</v>
       </c>
       <c r="F23" t="n">
-        <v>22218.97</v>
+        <v>136295.77</v>
       </c>
       <c r="G23" t="n">
-        <v>390.18</v>
+        <v>4606.18</v>
       </c>
       <c r="H23" t="n">
-        <v>15012.81</v>
+        <v>113579.81</v>
       </c>
       <c r="I23" t="n">
-        <v>21828.79</v>
+        <v>131689.59</v>
       </c>
       <c r="J23" t="n">
-        <v>21828.79</v>
+        <v>131689.59</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>1850</v>
+        <v>580</v>
       </c>
       <c r="F24" t="n">
-        <v>111094.83</v>
+        <v>167304.86</v>
       </c>
       <c r="G24" t="n">
-        <v>1950.9</v>
+        <v>5654.15</v>
       </c>
       <c r="H24" t="n">
-        <v>75064.07000000001</v>
+        <v>138459.2</v>
       </c>
       <c r="I24" t="n">
-        <v>109143.93</v>
+        <v>161650.71</v>
       </c>
       <c r="J24" t="n">
-        <v>109143.93</v>
+        <v>161650.71</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>2400</v>
+        <v>580</v>
       </c>
       <c r="F25" t="n">
-        <v>72061.50999999999</v>
+        <v>146391.76</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>8245.639999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>45038.44</v>
+        <v>121151.8</v>
       </c>
       <c r="I25" t="n">
-        <v>72061.50999999999</v>
+        <v>138146.12</v>
       </c>
       <c r="J25" t="n">
-        <v>72061.50999999999</v>
+        <v>138146.12</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="F26" t="n">
-        <v>273833.74</v>
+        <v>389416.49</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>8773.68</v>
       </c>
       <c r="H26" t="n">
-        <v>171146.09</v>
+        <v>335330.87</v>
       </c>
       <c r="I26" t="n">
-        <v>273833.74</v>
+        <v>380642.81</v>
       </c>
       <c r="J26" t="n">
-        <v>273833.74</v>
+        <v>380642.81</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F27" t="n">
-        <v>160336.86</v>
+        <v>1133995.25</v>
       </c>
       <c r="G27" t="n">
-        <v>7039.05</v>
+        <v>25549.29</v>
       </c>
       <c r="H27" t="n">
-        <v>106290.73</v>
+        <v>980752.65</v>
       </c>
       <c r="I27" t="n">
-        <v>153297.81</v>
+        <v>1108445.96</v>
       </c>
       <c r="J27" t="n">
-        <v>153297.81</v>
+        <v>1108445.96</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F28" t="n">
-        <v>288246.04</v>
+        <v>667056.03</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>37572.49</v>
       </c>
       <c r="H28" t="n">
-        <v>180153.78</v>
+        <v>576913.3199999999</v>
       </c>
       <c r="I28" t="n">
-        <v>288246.04</v>
+        <v>629483.54</v>
       </c>
       <c r="J28" t="n">
-        <v>288246.04</v>
+        <v>629483.54</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,37 +1545,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>8900</v>
+        <v>3600</v>
       </c>
       <c r="F29" t="n">
-        <v>427564.96</v>
+        <v>649027.49</v>
       </c>
       <c r="G29" t="n">
-        <v>11262.48</v>
+        <v>21934.21</v>
       </c>
       <c r="H29" t="n">
-        <v>283441.94</v>
+        <v>558884.78</v>
       </c>
       <c r="I29" t="n">
-        <v>416302.48</v>
+        <v>627093.28</v>
       </c>
       <c r="J29" t="n">
-        <v>416302.48</v>
+        <v>627093.28</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F30" t="n">
-        <v>1387184.07</v>
+        <v>733761.63</v>
       </c>
       <c r="G30" t="n">
-        <v>24359.86</v>
+        <v>41329.74</v>
       </c>
       <c r="H30" t="n">
-        <v>882753.5</v>
+        <v>634604.66</v>
       </c>
       <c r="I30" t="n">
-        <v>1362824.21</v>
+        <v>692431.89</v>
       </c>
       <c r="J30" t="n">
-        <v>1362824.21</v>
+        <v>692431.89</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>1850</v>
+        <v>580</v>
       </c>
       <c r="F31" t="n">
-        <v>166642.24</v>
+        <v>230044.19</v>
       </c>
       <c r="G31" t="n">
-        <v>2926.35</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>112596.11</v>
+        <v>190381.4</v>
       </c>
       <c r="I31" t="n">
-        <v>163715.89</v>
+        <v>230044.19</v>
       </c>
       <c r="J31" t="n">
-        <v>163715.89</v>
+        <v>230044.19</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>8900</v>
+        <v>420</v>
       </c>
       <c r="F32" t="n">
-        <v>160336.86</v>
+        <v>196871.67</v>
       </c>
       <c r="G32" t="n">
-        <v>4223.43</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>106290.73</v>
+        <v>164059.73</v>
       </c>
       <c r="I32" t="n">
-        <v>156113.43</v>
+        <v>196871.67</v>
       </c>
       <c r="J32" t="n">
-        <v>156113.43</v>
+        <v>196871.67</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>15400</v>
+        <v>1150</v>
       </c>
       <c r="F33" t="n">
-        <v>1942057.7</v>
+        <v>456122.1</v>
       </c>
       <c r="G33" t="n">
-        <v>51155.71</v>
+        <v>15414.88</v>
       </c>
       <c r="H33" t="n">
-        <v>1235854.9</v>
+        <v>388695.35</v>
       </c>
       <c r="I33" t="n">
-        <v>1890901.99</v>
+        <v>440707.22</v>
       </c>
       <c r="J33" t="n">
-        <v>1890901.99</v>
+        <v>440707.22</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>15400</v>
+        <v>580</v>
       </c>
       <c r="F34" t="n">
-        <v>1387184.07</v>
+        <v>104565.54</v>
       </c>
       <c r="G34" t="n">
-        <v>24359.86</v>
+        <v>3533.85</v>
       </c>
       <c r="H34" t="n">
-        <v>882753.5</v>
+        <v>86537</v>
       </c>
       <c r="I34" t="n">
-        <v>1362824.21</v>
+        <v>101031.69</v>
       </c>
       <c r="J34" t="n">
-        <v>1362824.21</v>
+        <v>101031.69</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,37 +1779,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E35" t="n">
-        <v>2400</v>
+        <v>980</v>
       </c>
       <c r="F35" t="n">
-        <v>230596.83</v>
+        <v>600711</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>33835.55</v>
       </c>
       <c r="H35" t="n">
-        <v>144123.02</v>
+        <v>514895.14</v>
       </c>
       <c r="I35" t="n">
-        <v>230596.83</v>
+        <v>566875.45</v>
       </c>
       <c r="J35" t="n">
-        <v>230596.83</v>
+        <v>566875.45</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,37 +1818,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="F36" t="n">
-        <v>273833.74</v>
+        <v>519221.99</v>
       </c>
       <c r="G36" t="n">
-        <v>4808.7</v>
+        <v>17547.37</v>
       </c>
       <c r="H36" t="n">
-        <v>171146.09</v>
+        <v>447107.83</v>
       </c>
       <c r="I36" t="n">
-        <v>269025.04</v>
+        <v>501674.62</v>
       </c>
       <c r="J36" t="n">
-        <v>269025.04</v>
+        <v>501674.62</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,37 +1857,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E37" t="n">
-        <v>15400</v>
+        <v>420</v>
       </c>
       <c r="F37" t="n">
-        <v>2127015.58</v>
+        <v>227159.62</v>
       </c>
       <c r="G37" t="n">
-        <v>37351.79</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1353555.37</v>
+        <v>189299.68</v>
       </c>
       <c r="I37" t="n">
-        <v>2089663.79</v>
+        <v>227159.62</v>
       </c>
       <c r="J37" t="n">
-        <v>2089663.79</v>
+        <v>227159.62</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1896,37 +1896,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>2400</v>
+        <v>580</v>
       </c>
       <c r="F38" t="n">
-        <v>129710.72</v>
+        <v>104565.54</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>81069.2</v>
+        <v>86537</v>
       </c>
       <c r="I38" t="n">
-        <v>129710.72</v>
+        <v>104565.54</v>
       </c>
       <c r="J38" t="n">
-        <v>129710.72</v>
+        <v>104565.54</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>1850</v>
+        <v>3600</v>
       </c>
       <c r="F39" t="n">
-        <v>222189.66</v>
+        <v>1168249.48</v>
       </c>
       <c r="G39" t="n">
-        <v>5852.69</v>
+        <v>26321.05</v>
       </c>
       <c r="H39" t="n">
-        <v>150128.15</v>
+        <v>1005992.61</v>
       </c>
       <c r="I39" t="n">
-        <v>216336.97</v>
+        <v>1141928.43</v>
       </c>
       <c r="J39" t="n">
-        <v>216336.97</v>
+        <v>1141928.43</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>15400</v>
+        <v>280</v>
       </c>
       <c r="F40" t="n">
-        <v>2311973.46</v>
+        <v>30287.95</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>682.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1471255.84</v>
+        <v>25420.24</v>
       </c>
       <c r="I40" t="n">
-        <v>2311973.46</v>
+        <v>29605.55</v>
       </c>
       <c r="J40" t="n">
-        <v>2311973.46</v>
+        <v>29605.55</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F41" t="n">
-        <v>31226.65</v>
+        <v>1067289.65</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>60115.98</v>
       </c>
       <c r="H41" t="n">
-        <v>21138.04</v>
+        <v>923061.3199999999</v>
       </c>
       <c r="I41" t="n">
-        <v>31226.65</v>
+        <v>1007173.67</v>
       </c>
       <c r="J41" t="n">
-        <v>31226.65</v>
+        <v>1007173.67</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>15400</v>
+        <v>420</v>
       </c>
       <c r="F42" t="n">
-        <v>2034536.64</v>
+        <v>45431.92</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1294705.14</v>
+        <v>37859.94</v>
       </c>
       <c r="I42" t="n">
-        <v>2034536.64</v>
+        <v>45431.92</v>
       </c>
       <c r="J42" t="n">
-        <v>2034536.64</v>
+        <v>45431.92</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4200</v>
+        <v>980</v>
       </c>
       <c r="F43" t="n">
-        <v>529652.1</v>
+        <v>106007.82</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>3582.59</v>
       </c>
       <c r="H43" t="n">
-        <v>353101.4</v>
+        <v>90863.85000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>529652.1</v>
+        <v>102425.23</v>
       </c>
       <c r="J43" t="n">
-        <v>529652.1</v>
+        <v>102425.23</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>21500</v>
+        <v>3600</v>
       </c>
       <c r="F44" t="n">
-        <v>258220.41</v>
+        <v>519221.99</v>
       </c>
       <c r="G44" t="n">
-        <v>11336.3</v>
+        <v>17547.37</v>
       </c>
       <c r="H44" t="n">
-        <v>170545.57</v>
+        <v>447107.83</v>
       </c>
       <c r="I44" t="n">
-        <v>246884.11</v>
+        <v>501674.62</v>
       </c>
       <c r="J44" t="n">
-        <v>246884.11</v>
+        <v>501674.62</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,37 +2169,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>8900</v>
+        <v>280</v>
       </c>
       <c r="F45" t="n">
-        <v>160336.86</v>
+        <v>100959.83</v>
       </c>
       <c r="G45" t="n">
-        <v>2815.62</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>106290.73</v>
+        <v>84734.14</v>
       </c>
       <c r="I45" t="n">
-        <v>157521.24</v>
+        <v>100959.83</v>
       </c>
       <c r="J45" t="n">
-        <v>157521.24</v>
+        <v>100959.83</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F46" t="n">
-        <v>86473.81</v>
+        <v>133411.21</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3005.8</v>
       </c>
       <c r="H46" t="n">
-        <v>54046.13</v>
+        <v>115382.66</v>
       </c>
       <c r="I46" t="n">
-        <v>86473.81</v>
+        <v>130405.41</v>
       </c>
       <c r="J46" t="n">
-        <v>86473.81</v>
+        <v>130405.41</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F47" t="n">
-        <v>66356.64</v>
+        <v>933878.4399999999</v>
       </c>
       <c r="G47" t="n">
-        <v>2913.17</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>44918.34</v>
+        <v>807678.65</v>
       </c>
       <c r="I47" t="n">
-        <v>63443.47</v>
+        <v>933878.4399999999</v>
       </c>
       <c r="J47" t="n">
-        <v>63443.47</v>
+        <v>933878.4399999999</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E48" t="n">
-        <v>15400</v>
+        <v>420</v>
       </c>
       <c r="F48" t="n">
-        <v>554873.63</v>
+        <v>212015.65</v>
       </c>
       <c r="G48" t="n">
-        <v>9743.940000000001</v>
+        <v>11941.96</v>
       </c>
       <c r="H48" t="n">
-        <v>353101.4</v>
+        <v>176679.71</v>
       </c>
       <c r="I48" t="n">
-        <v>545129.6899999999</v>
+        <v>200073.69</v>
       </c>
       <c r="J48" t="n">
-        <v>545129.6899999999</v>
+        <v>200073.69</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>21500</v>
+        <v>980</v>
       </c>
       <c r="F49" t="n">
-        <v>1291102.06</v>
+        <v>212015.65</v>
       </c>
       <c r="G49" t="n">
-        <v>22672.6</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>852727.87</v>
+        <v>181727.7</v>
       </c>
       <c r="I49" t="n">
-        <v>1268429.46</v>
+        <v>212015.65</v>
       </c>
       <c r="J49" t="n">
-        <v>1268429.46</v>
+        <v>212015.65</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,37 +2364,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>4200</v>
+        <v>420</v>
       </c>
       <c r="F50" t="n">
-        <v>378322.93</v>
+        <v>121151.8</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>4094.39</v>
       </c>
       <c r="H50" t="n">
-        <v>252215.29</v>
+        <v>100959.83</v>
       </c>
       <c r="I50" t="n">
-        <v>378322.93</v>
+        <v>117057.41</v>
       </c>
       <c r="J50" t="n">
-        <v>378322.93</v>
+        <v>117057.41</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E51" t="n">
-        <v>1200</v>
+        <v>980</v>
       </c>
       <c r="F51" t="n">
-        <v>158535.32</v>
+        <v>530039.12</v>
       </c>
       <c r="G51" t="n">
-        <v>4175.98</v>
+        <v>11941.96</v>
       </c>
       <c r="H51" t="n">
-        <v>108332.47</v>
+        <v>454319.24</v>
       </c>
       <c r="I51" t="n">
-        <v>154359.34</v>
+        <v>518097.16</v>
       </c>
       <c r="J51" t="n">
-        <v>154359.34</v>
+        <v>518097.16</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,37 +2442,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F52" t="n">
-        <v>11710</v>
+        <v>66705.60000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>308.45</v>
+        <v>2254.35</v>
       </c>
       <c r="H52" t="n">
-        <v>7926.77</v>
+        <v>57691.33</v>
       </c>
       <c r="I52" t="n">
-        <v>11401.55</v>
+        <v>64451.25</v>
       </c>
       <c r="J52" t="n">
-        <v>11401.55</v>
+        <v>64451.25</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,12 +2481,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -2496,22 +2496,22 @@
         <v>18</v>
       </c>
       <c r="E53" t="n">
-        <v>15400</v>
+        <v>280</v>
       </c>
       <c r="F53" t="n">
-        <v>1664620.89</v>
+        <v>181727.7</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1059304.2</v>
+        <v>152521.46</v>
       </c>
       <c r="I53" t="n">
-        <v>1664620.89</v>
+        <v>181727.7</v>
       </c>
       <c r="J53" t="n">
-        <v>1664620.89</v>
+        <v>181727.7</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="F54" t="n">
-        <v>85873.3</v>
+        <v>250957.3</v>
       </c>
       <c r="G54" t="n">
-        <v>1507.99</v>
+        <v>14135.38</v>
       </c>
       <c r="H54" t="n">
-        <v>58129.62</v>
+        <v>207688.8</v>
       </c>
       <c r="I54" t="n">
-        <v>84365.31</v>
+        <v>236821.92</v>
       </c>
       <c r="J54" t="n">
-        <v>84365.31</v>
+        <v>236821.92</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E55" t="n">
-        <v>2400</v>
+        <v>280</v>
       </c>
       <c r="F55" t="n">
-        <v>302658.34</v>
+        <v>141343.76</v>
       </c>
       <c r="G55" t="n">
-        <v>5314.88</v>
+        <v>3184.52</v>
       </c>
       <c r="H55" t="n">
-        <v>189161.46</v>
+        <v>118627.8</v>
       </c>
       <c r="I55" t="n">
-        <v>297343.46</v>
+        <v>138159.24</v>
       </c>
       <c r="J55" t="n">
-        <v>297343.46</v>
+        <v>138159.24</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,37 +2598,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>1200</v>
+        <v>3600</v>
       </c>
       <c r="F56" t="n">
-        <v>115298.42</v>
+        <v>1298054.98</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>78787.25</v>
+        <v>1117769.56</v>
       </c>
       <c r="I56" t="n">
-        <v>115298.42</v>
+        <v>1298054.98</v>
       </c>
       <c r="J56" t="n">
-        <v>115298.42</v>
+        <v>1298054.98</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
-        <v>650</v>
+        <v>3600</v>
       </c>
       <c r="F57" t="n">
-        <v>78066.64</v>
+        <v>2076887.96</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>52845.11</v>
+        <v>1788431.3</v>
       </c>
       <c r="I57" t="n">
-        <v>78066.64</v>
+        <v>2076887.96</v>
       </c>
       <c r="J57" t="n">
-        <v>78066.64</v>
+        <v>2076887.96</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E58" t="n">
-        <v>4200</v>
+        <v>580</v>
       </c>
       <c r="F58" t="n">
-        <v>529652.1</v>
+        <v>397349.05</v>
       </c>
       <c r="G58" t="n">
-        <v>13951.56</v>
+        <v>8952.41</v>
       </c>
       <c r="H58" t="n">
-        <v>353101.4</v>
+        <v>328840.59</v>
       </c>
       <c r="I58" t="n">
-        <v>515700.54</v>
+        <v>388396.64</v>
       </c>
       <c r="J58" t="n">
-        <v>515700.54</v>
+        <v>388396.64</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>15400</v>
+        <v>280</v>
       </c>
       <c r="F59" t="n">
-        <v>1942057.7</v>
+        <v>100959.83</v>
       </c>
       <c r="G59" t="n">
-        <v>51155.71</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1235854.9</v>
+        <v>84734.14</v>
       </c>
       <c r="I59" t="n">
-        <v>1890901.99</v>
+        <v>100959.83</v>
       </c>
       <c r="J59" t="n">
-        <v>1890901.99</v>
+        <v>100959.83</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,37 +2754,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F60" t="n">
-        <v>106891.24</v>
+        <v>66705.60000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>3757.25</v>
       </c>
       <c r="H60" t="n">
-        <v>70860.49000000001</v>
+        <v>57691.33</v>
       </c>
       <c r="I60" t="n">
-        <v>106891.24</v>
+        <v>62948.35</v>
       </c>
       <c r="J60" t="n">
-        <v>106891.24</v>
+        <v>62948.35</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,37 +2793,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>21500</v>
+        <v>420</v>
       </c>
       <c r="F61" t="n">
-        <v>516440.82</v>
+        <v>242303.6</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>5459.18</v>
       </c>
       <c r="H61" t="n">
-        <v>341091.15</v>
+        <v>201919.66</v>
       </c>
       <c r="I61" t="n">
-        <v>516440.82</v>
+        <v>236844.42</v>
       </c>
       <c r="J61" t="n">
-        <v>516440.82</v>
+        <v>236844.42</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,37 +2832,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E62" t="n">
-        <v>8900</v>
+        <v>420</v>
       </c>
       <c r="F62" t="n">
-        <v>694793.0600000001</v>
+        <v>181727.7</v>
       </c>
       <c r="G62" t="n">
-        <v>18301.53</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>460593.15</v>
+        <v>151439.75</v>
       </c>
       <c r="I62" t="n">
-        <v>676491.53</v>
+        <v>181727.7</v>
       </c>
       <c r="J62" t="n">
-        <v>676491.53</v>
+        <v>181727.7</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,37 +2871,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>2400</v>
+        <v>420</v>
       </c>
       <c r="F63" t="n">
-        <v>273833.74</v>
+        <v>136295.77</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>171146.09</v>
+        <v>113579.81</v>
       </c>
       <c r="I63" t="n">
-        <v>273833.74</v>
+        <v>136295.77</v>
       </c>
       <c r="J63" t="n">
-        <v>273833.74</v>
+        <v>136295.77</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,37 +2910,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>2400</v>
+        <v>280</v>
       </c>
       <c r="F64" t="n">
-        <v>302658.34</v>
+        <v>20191.97</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>454.93</v>
       </c>
       <c r="H64" t="n">
-        <v>189161.46</v>
+        <v>16946.83</v>
       </c>
       <c r="I64" t="n">
-        <v>302658.34</v>
+        <v>19737.04</v>
       </c>
       <c r="J64" t="n">
-        <v>302658.34</v>
+        <v>19737.04</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E65" t="n">
-        <v>21500</v>
+        <v>1150</v>
       </c>
       <c r="F65" t="n">
-        <v>2582204.12</v>
+        <v>787847.26</v>
       </c>
       <c r="G65" t="n">
-        <v>68017.8</v>
+        <v>17750.46</v>
       </c>
       <c r="H65" t="n">
-        <v>1705455.74</v>
+        <v>671382.88</v>
       </c>
       <c r="I65" t="n">
-        <v>2514186.32</v>
+        <v>770096.8</v>
       </c>
       <c r="J65" t="n">
-        <v>2514186.32</v>
+        <v>770096.8</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>1850</v>
+        <v>1150</v>
       </c>
       <c r="F66" t="n">
-        <v>255518.11</v>
+        <v>414656.45</v>
       </c>
       <c r="G66" t="n">
-        <v>4487.07</v>
+        <v>9342.35</v>
       </c>
       <c r="H66" t="n">
-        <v>172647.37</v>
+        <v>353359.41</v>
       </c>
       <c r="I66" t="n">
-        <v>251031.04</v>
+        <v>405314.1</v>
       </c>
       <c r="J66" t="n">
-        <v>251031.04</v>
+        <v>405314.1</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>21500</v>
+        <v>980</v>
       </c>
       <c r="F67" t="n">
-        <v>1936653.09</v>
+        <v>247351.59</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1279091.81</v>
+        <v>212015.65</v>
       </c>
       <c r="I67" t="n">
-        <v>1936653.09</v>
+        <v>247351.59</v>
       </c>
       <c r="J67" t="n">
-        <v>1936653.09</v>
+        <v>247351.59</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E68" t="n">
-        <v>650</v>
+        <v>420</v>
       </c>
       <c r="F68" t="n">
-        <v>15613.33</v>
+        <v>257447.57</v>
       </c>
       <c r="G68" t="n">
-        <v>274.18</v>
+        <v>5800.38</v>
       </c>
       <c r="H68" t="n">
-        <v>10569.02</v>
+        <v>214539.64</v>
       </c>
       <c r="I68" t="n">
-        <v>15339.15</v>
+        <v>251647.19</v>
       </c>
       <c r="J68" t="n">
-        <v>15339.15</v>
+        <v>251647.19</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F69" t="n">
-        <v>7806.66</v>
+        <v>1067289.65</v>
       </c>
       <c r="G69" t="n">
-        <v>205.64</v>
+        <v>24046.39</v>
       </c>
       <c r="H69" t="n">
-        <v>5284.51</v>
+        <v>923061.3199999999</v>
       </c>
       <c r="I69" t="n">
-        <v>7601.02</v>
+        <v>1043243.26</v>
       </c>
       <c r="J69" t="n">
-        <v>7601.02</v>
+        <v>1043243.26</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3144,12 +3144,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -3159,22 +3159,22 @@
         <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>1200</v>
+        <v>3600</v>
       </c>
       <c r="F70" t="n">
-        <v>28824.6</v>
+        <v>519221.99</v>
       </c>
       <c r="G70" t="n">
-        <v>759.27</v>
+        <v>17547.37</v>
       </c>
       <c r="H70" t="n">
-        <v>19696.81</v>
+        <v>447107.83</v>
       </c>
       <c r="I70" t="n">
-        <v>28065.33</v>
+        <v>501674.62</v>
       </c>
       <c r="J70" t="n">
-        <v>28065.33</v>
+        <v>501674.62</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>1200</v>
+        <v>980</v>
       </c>
       <c r="F71" t="n">
-        <v>151329.17</v>
+        <v>282687.53</v>
       </c>
       <c r="G71" t="n">
-        <v>6643.6</v>
+        <v>9553.57</v>
       </c>
       <c r="H71" t="n">
-        <v>103408.27</v>
+        <v>242303.6</v>
       </c>
       <c r="I71" t="n">
-        <v>144685.57</v>
+        <v>273133.96</v>
       </c>
       <c r="J71" t="n">
-        <v>144685.57</v>
+        <v>273133.96</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E72" t="n">
-        <v>1850</v>
+        <v>1150</v>
       </c>
       <c r="F72" t="n">
-        <v>122204.31</v>
+        <v>539053.39</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>82570.48</v>
+        <v>459367.23</v>
       </c>
       <c r="I72" t="n">
-        <v>122204.31</v>
+        <v>539053.39</v>
       </c>
       <c r="J72" t="n">
-        <v>122204.31</v>
+        <v>539053.39</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,37 +3261,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>1200</v>
+        <v>420</v>
       </c>
       <c r="F73" t="n">
-        <v>21618.45</v>
+        <v>60575.9</v>
       </c>
       <c r="G73" t="n">
-        <v>949.09</v>
+        <v>2047.19</v>
       </c>
       <c r="H73" t="n">
-        <v>14772.61</v>
+        <v>50479.92</v>
       </c>
       <c r="I73" t="n">
-        <v>20669.36</v>
+        <v>58528.71</v>
       </c>
       <c r="J73" t="n">
-        <v>20669.36</v>
+        <v>58528.71</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,37 +3300,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E74" t="n">
-        <v>1200</v>
+        <v>280</v>
       </c>
       <c r="F74" t="n">
-        <v>57649.21</v>
+        <v>90863.85000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>1012.36</v>
+        <v>5117.98</v>
       </c>
       <c r="H74" t="n">
-        <v>39393.63</v>
+        <v>76260.73</v>
       </c>
       <c r="I74" t="n">
-        <v>56636.85</v>
+        <v>85745.87</v>
       </c>
       <c r="J74" t="n">
-        <v>56636.85</v>
+        <v>85745.87</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E75" t="n">
-        <v>8900</v>
+        <v>3600</v>
       </c>
       <c r="F75" t="n">
-        <v>1068912.4</v>
+        <v>1557665.97</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>708604.85</v>
+        <v>1341323.48</v>
       </c>
       <c r="I75" t="n">
-        <v>1068912.4</v>
+        <v>1557665.97</v>
       </c>
       <c r="J75" t="n">
-        <v>1068912.4</v>
+        <v>1557665.97</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>8900</v>
+        <v>580</v>
       </c>
       <c r="F76" t="n">
-        <v>267228.1</v>
+        <v>20913.11</v>
       </c>
       <c r="G76" t="n">
-        <v>11731.75</v>
+        <v>1177.95</v>
       </c>
       <c r="H76" t="n">
-        <v>177151.21</v>
+        <v>17307.4</v>
       </c>
       <c r="I76" t="n">
-        <v>255496.35</v>
+        <v>19735.16</v>
       </c>
       <c r="J76" t="n">
-        <v>255496.35</v>
+        <v>19735.16</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,37 +3417,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>8900</v>
+        <v>420</v>
       </c>
       <c r="F77" t="n">
-        <v>213782.48</v>
+        <v>121151.8</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>141720.97</v>
+        <v>100959.83</v>
       </c>
       <c r="I77" t="n">
-        <v>213782.48</v>
+        <v>121151.8</v>
       </c>
       <c r="J77" t="n">
-        <v>213782.48</v>
+        <v>121151.8</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E78" t="n">
-        <v>1850</v>
+        <v>280</v>
       </c>
       <c r="F78" t="n">
-        <v>133313.79</v>
+        <v>100959.83</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>3411.99</v>
       </c>
       <c r="H78" t="n">
-        <v>90076.89</v>
+        <v>84734.14</v>
       </c>
       <c r="I78" t="n">
-        <v>133313.79</v>
+        <v>97547.84</v>
       </c>
       <c r="J78" t="n">
-        <v>133313.79</v>
+        <v>97547.84</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>650</v>
+        <v>980</v>
       </c>
       <c r="F79" t="n">
-        <v>3903.33</v>
+        <v>70671.88</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2642.26</v>
+        <v>60575.9</v>
       </c>
       <c r="I79" t="n">
-        <v>3903.33</v>
+        <v>70671.88</v>
       </c>
       <c r="J79" t="n">
-        <v>3903.33</v>
+        <v>70671.88</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,37 +3534,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>1850</v>
+        <v>580</v>
       </c>
       <c r="F80" t="n">
-        <v>55547.41</v>
+        <v>83652.42999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>1463.17</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>37532.04</v>
+        <v>69229.60000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>54084.24</v>
+        <v>83652.42999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>54084.24</v>
+        <v>83652.42999999999</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>4200</v>
+        <v>420</v>
       </c>
       <c r="F81" t="n">
-        <v>605316.6899999999</v>
+        <v>75719.87</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2558.99</v>
       </c>
       <c r="H81" t="n">
-        <v>403544.46</v>
+        <v>63099.89</v>
       </c>
       <c r="I81" t="n">
-        <v>605316.6899999999</v>
+        <v>73160.88</v>
       </c>
       <c r="J81" t="n">
-        <v>605316.6899999999</v>
+        <v>73160.88</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E82" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F82" t="n">
-        <v>3227755.15</v>
+        <v>1200700.85</v>
       </c>
       <c r="G82" t="n">
-        <v>56681.5</v>
+        <v>40578.29</v>
       </c>
       <c r="H82" t="n">
-        <v>2131819.68</v>
+        <v>1038443.98</v>
       </c>
       <c r="I82" t="n">
-        <v>3171073.65</v>
+        <v>1160122.56</v>
       </c>
       <c r="J82" t="n">
-        <v>3171073.65</v>
+        <v>1160122.56</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>4200</v>
+        <v>580</v>
       </c>
       <c r="F83" t="n">
-        <v>378322.93</v>
+        <v>83652.42999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>16609</v>
+        <v>2827.08</v>
       </c>
       <c r="H83" t="n">
-        <v>252215.29</v>
+        <v>69229.60000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>361713.93</v>
+        <v>80825.35000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>361713.93</v>
+        <v>80825.35000000001</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
         <v>1850</v>
       </c>
       <c r="F84" t="n">
-        <v>266627.59</v>
+        <v>133411.21</v>
       </c>
       <c r="G84" t="n">
-        <v>11705.39</v>
+        <v>3005.8</v>
       </c>
       <c r="H84" t="n">
-        <v>180153.78</v>
+        <v>115382.66</v>
       </c>
       <c r="I84" t="n">
-        <v>254922.2</v>
+        <v>130405.41</v>
       </c>
       <c r="J84" t="n">
-        <v>254922.2</v>
+        <v>130405.41</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E85" t="n">
-        <v>21500</v>
+        <v>580</v>
       </c>
       <c r="F85" t="n">
-        <v>2711314.33</v>
+        <v>313696.62</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1790728.53</v>
+        <v>259611</v>
       </c>
       <c r="I85" t="n">
-        <v>2711314.33</v>
+        <v>313696.62</v>
       </c>
       <c r="J85" t="n">
-        <v>2711314.33</v>
+        <v>313696.62</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E86" t="n">
-        <v>21500</v>
+        <v>1150</v>
       </c>
       <c r="F86" t="n">
-        <v>1678432.68</v>
+        <v>497587.74</v>
       </c>
       <c r="G86" t="n">
-        <v>44211.57</v>
+        <v>28027.05</v>
       </c>
       <c r="H86" t="n">
-        <v>1108546.23</v>
+        <v>424031.29</v>
       </c>
       <c r="I86" t="n">
-        <v>1634221.11</v>
+        <v>469560.69</v>
       </c>
       <c r="J86" t="n">
-        <v>1634221.11</v>
+        <v>469560.69</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,37 +3807,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E87" t="n">
-        <v>4200</v>
+        <v>1150</v>
       </c>
       <c r="F87" t="n">
-        <v>403544.46</v>
+        <v>539053.39</v>
       </c>
       <c r="G87" t="n">
-        <v>10629.76</v>
+        <v>12145.05</v>
       </c>
       <c r="H87" t="n">
-        <v>269029.64</v>
+        <v>459367.23</v>
       </c>
       <c r="I87" t="n">
-        <v>392914.7</v>
+        <v>526908.34</v>
       </c>
       <c r="J87" t="n">
-        <v>392914.7</v>
+        <v>526908.34</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E88" t="n">
-        <v>4200</v>
+        <v>1150</v>
       </c>
       <c r="F88" t="n">
-        <v>277436.81</v>
+        <v>621984.6800000001</v>
       </c>
       <c r="G88" t="n">
-        <v>12179.93</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>184957.88</v>
+        <v>530039.12</v>
       </c>
       <c r="I88" t="n">
-        <v>265256.88</v>
+        <v>621984.6800000001</v>
       </c>
       <c r="J88" t="n">
-        <v>265256.88</v>
+        <v>621984.6800000001</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,37 +3885,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E89" t="n">
-        <v>4200</v>
+        <v>280</v>
       </c>
       <c r="F89" t="n">
-        <v>126107.64</v>
+        <v>201919.66</v>
       </c>
       <c r="G89" t="n">
-        <v>2214.53</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>84071.75999999999</v>
+        <v>169468.29</v>
       </c>
       <c r="I89" t="n">
-        <v>123893.11</v>
+        <v>201919.66</v>
       </c>
       <c r="J89" t="n">
-        <v>123893.11</v>
+        <v>201919.66</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E90" t="n">
-        <v>650</v>
+        <v>3600</v>
       </c>
       <c r="F90" t="n">
-        <v>50743.31</v>
+        <v>1427860.47</v>
       </c>
       <c r="G90" t="n">
-        <v>2227.71</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>34349.32</v>
+        <v>1229546.52</v>
       </c>
       <c r="I90" t="n">
-        <v>48515.6</v>
+        <v>1427860.47</v>
       </c>
       <c r="J90" t="n">
-        <v>48515.6</v>
+        <v>1427860.47</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E91" t="n">
-        <v>15400</v>
+        <v>3600</v>
       </c>
       <c r="F91" t="n">
-        <v>1387184.07</v>
+        <v>2466304.46</v>
       </c>
       <c r="G91" t="n">
-        <v>60899.65</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>882753.5</v>
+        <v>2123762.17</v>
       </c>
       <c r="I91" t="n">
-        <v>1326284.42</v>
+        <v>2466304.46</v>
       </c>
       <c r="J91" t="n">
-        <v>1326284.42</v>
+        <v>2466304.46</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E92" t="n">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="F92" t="n">
-        <v>57649.21</v>
+        <v>2336498.96</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>36030.76</v>
+        <v>2011985.21</v>
       </c>
       <c r="I92" t="n">
-        <v>57649.21</v>
+        <v>2336498.96</v>
       </c>
       <c r="J92" t="n">
-        <v>57649.21</v>
+        <v>2336498.96</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E93" t="n">
-        <v>1200</v>
+        <v>3600</v>
       </c>
       <c r="F93" t="n">
-        <v>100886.11</v>
+        <v>1038443.98</v>
       </c>
       <c r="G93" t="n">
-        <v>2657.44</v>
+        <v>23396.49</v>
       </c>
       <c r="H93" t="n">
-        <v>68938.84</v>
+        <v>894215.65</v>
       </c>
       <c r="I93" t="n">
-        <v>98228.67</v>
+        <v>1015047.49</v>
       </c>
       <c r="J93" t="n">
-        <v>98228.67</v>
+        <v>1015047.49</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E94" t="n">
-        <v>1200</v>
+        <v>3600</v>
       </c>
       <c r="F94" t="n">
-        <v>100886.11</v>
+        <v>2596109.95</v>
       </c>
       <c r="G94" t="n">
-        <v>1771.63</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>68938.84</v>
+        <v>2235539.13</v>
       </c>
       <c r="I94" t="n">
-        <v>99114.48</v>
+        <v>2596109.95</v>
       </c>
       <c r="J94" t="n">
-        <v>99114.48</v>
+        <v>2596109.95</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,37 +4119,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>21500</v>
+        <v>3600</v>
       </c>
       <c r="F95" t="n">
-        <v>1678432.68</v>
+        <v>649027.49</v>
       </c>
       <c r="G95" t="n">
-        <v>44211.57</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1108546.23</v>
+        <v>558884.78</v>
       </c>
       <c r="I95" t="n">
-        <v>1634221.11</v>
+        <v>649027.49</v>
       </c>
       <c r="J95" t="n">
-        <v>1634221.11</v>
+        <v>649027.49</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="F96" t="n">
-        <v>277436.81</v>
+        <v>778832.99</v>
       </c>
       <c r="G96" t="n">
-        <v>7307.96</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>184957.88</v>
+        <v>670661.74</v>
       </c>
       <c r="I96" t="n">
-        <v>270128.85</v>
+        <v>778832.99</v>
       </c>
       <c r="J96" t="n">
-        <v>270128.85</v>
+        <v>778832.99</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>15400</v>
+        <v>980</v>
       </c>
       <c r="F97" t="n">
-        <v>1109747.26</v>
+        <v>35335.94</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>796.13</v>
       </c>
       <c r="H97" t="n">
-        <v>706202.8</v>
+        <v>30287.95</v>
       </c>
       <c r="I97" t="n">
-        <v>1109747.26</v>
+        <v>34539.81</v>
       </c>
       <c r="J97" t="n">
-        <v>1109747.26</v>
+        <v>34539.81</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,37 +4236,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E98" t="n">
-        <v>21500</v>
+        <v>420</v>
       </c>
       <c r="F98" t="n">
-        <v>387330.62</v>
+        <v>166583.72</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>255818.36</v>
+        <v>138819.77</v>
       </c>
       <c r="I98" t="n">
-        <v>387330.62</v>
+        <v>166583.72</v>
       </c>
       <c r="J98" t="n">
-        <v>387330.62</v>
+        <v>166583.72</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F99" t="n">
-        <v>75664.59</v>
+        <v>133411.21</v>
       </c>
       <c r="G99" t="n">
-        <v>1993.08</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>50443.06</v>
+        <v>115382.66</v>
       </c>
       <c r="I99" t="n">
-        <v>73671.50999999999</v>
+        <v>133411.21</v>
       </c>
       <c r="J99" t="n">
-        <v>73671.50999999999</v>
+        <v>133411.21</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>650</v>
+        <v>420</v>
       </c>
       <c r="F100" t="n">
-        <v>19516.66</v>
+        <v>60575.9</v>
       </c>
       <c r="G100" t="n">
-        <v>856.8099999999999</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>13211.28</v>
+        <v>50479.92</v>
       </c>
       <c r="I100" t="n">
-        <v>18659.85</v>
+        <v>60575.9</v>
       </c>
       <c r="J100" t="n">
-        <v>18659.85</v>
+        <v>60575.9</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,37 +4353,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>45858</v>
       </c>
       <c r="D101" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E101" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="F101" t="n">
-        <v>85873.3</v>
+        <v>250957.3</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>14135.38</v>
       </c>
       <c r="H101" t="n">
-        <v>58129.62</v>
+        <v>207688.8</v>
       </c>
       <c r="I101" t="n">
-        <v>85873.3</v>
+        <v>236821.92</v>
       </c>
       <c r="J101" t="n">
-        <v>85873.3</v>
+        <v>236821.92</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,37 +4392,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E102" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="F102" t="n">
-        <v>85873.3</v>
+        <v>355522.84</v>
       </c>
       <c r="G102" t="n">
-        <v>2261.99</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>58129.62</v>
+        <v>294225.79</v>
       </c>
       <c r="I102" t="n">
-        <v>83611.31</v>
+        <v>355522.84</v>
       </c>
       <c r="J102" t="n">
-        <v>83611.31</v>
+        <v>355522.84</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E103" t="n">
-        <v>1850</v>
+        <v>280</v>
       </c>
       <c r="F103" t="n">
-        <v>111094.83</v>
+        <v>171631.71</v>
       </c>
       <c r="G103" t="n">
-        <v>4877.25</v>
+        <v>3866.92</v>
       </c>
       <c r="H103" t="n">
-        <v>75064.07000000001</v>
+        <v>144048.05</v>
       </c>
       <c r="I103" t="n">
-        <v>106217.58</v>
+        <v>167764.79</v>
       </c>
       <c r="J103" t="n">
-        <v>106217.58</v>
+        <v>167764.79</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="F104" t="n">
-        <v>15613.33</v>
+        <v>10095.98</v>
       </c>
       <c r="G104" t="n">
-        <v>685.45</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>10569.02</v>
+        <v>8473.41</v>
       </c>
       <c r="I104" t="n">
-        <v>14927.88</v>
+        <v>10095.98</v>
       </c>
       <c r="J104" t="n">
-        <v>14927.88</v>
+        <v>10095.98</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,37 +4509,37 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E105" t="n">
-        <v>1200</v>
+        <v>3600</v>
       </c>
       <c r="F105" t="n">
-        <v>36030.76</v>
+        <v>1687471.47</v>
       </c>
       <c r="G105" t="n">
-        <v>949.09</v>
+        <v>57028.95</v>
       </c>
       <c r="H105" t="n">
-        <v>24621.02</v>
+        <v>1453100.43</v>
       </c>
       <c r="I105" t="n">
-        <v>35081.67</v>
+        <v>1630442.52</v>
       </c>
       <c r="J105" t="n">
-        <v>35081.67</v>
+        <v>1630442.52</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E106" t="n">
-        <v>4200</v>
+        <v>580</v>
       </c>
       <c r="F106" t="n">
-        <v>302658.34</v>
+        <v>313696.62</v>
       </c>
       <c r="G106" t="n">
-        <v>13287.2</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>201772.23</v>
+        <v>259611</v>
       </c>
       <c r="I106" t="n">
-        <v>289371.14</v>
+        <v>313696.62</v>
       </c>
       <c r="J106" t="n">
-        <v>289371.14</v>
+        <v>313696.62</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,37 +4587,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E107" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F107" t="n">
-        <v>630538.22</v>
+        <v>1334112.06</v>
       </c>
       <c r="G107" t="n">
-        <v>11072.66</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>420358.81</v>
+        <v>1153826.65</v>
       </c>
       <c r="I107" t="n">
-        <v>619465.5600000001</v>
+        <v>1334112.06</v>
       </c>
       <c r="J107" t="n">
-        <v>619465.5600000001</v>
+        <v>1334112.06</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E108" t="n">
-        <v>1200</v>
+        <v>980</v>
       </c>
       <c r="F108" t="n">
-        <v>100886.11</v>
+        <v>318023.47</v>
       </c>
       <c r="G108" t="n">
-        <v>4429.07</v>
+        <v>17912.94</v>
       </c>
       <c r="H108" t="n">
-        <v>68938.84</v>
+        <v>272591.55</v>
       </c>
       <c r="I108" t="n">
-        <v>96457.03999999999</v>
+        <v>300110.53</v>
       </c>
       <c r="J108" t="n">
-        <v>96457.03999999999</v>
+        <v>300110.53</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,12 +4665,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
@@ -4680,22 +4680,22 @@
         <v>20</v>
       </c>
       <c r="E109" t="n">
-        <v>1850</v>
+        <v>580</v>
       </c>
       <c r="F109" t="n">
-        <v>222189.66</v>
+        <v>418262.16</v>
       </c>
       <c r="G109" t="n">
-        <v>3901.8</v>
+        <v>23558.97</v>
       </c>
       <c r="H109" t="n">
-        <v>150128.15</v>
+        <v>346147.99</v>
       </c>
       <c r="I109" t="n">
-        <v>218287.86</v>
+        <v>394703.19</v>
       </c>
       <c r="J109" t="n">
-        <v>218287.86</v>
+        <v>394703.19</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E110" t="n">
-        <v>8900</v>
+        <v>580</v>
       </c>
       <c r="F110" t="n">
-        <v>481010.58</v>
+        <v>355522.84</v>
       </c>
       <c r="G110" t="n">
-        <v>8446.860000000001</v>
+        <v>20025.12</v>
       </c>
       <c r="H110" t="n">
-        <v>318872.18</v>
+        <v>294225.79</v>
       </c>
       <c r="I110" t="n">
-        <v>472563.72</v>
+        <v>335497.72</v>
       </c>
       <c r="J110" t="n">
-        <v>472563.72</v>
+        <v>335497.72</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,37 +4743,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E111" t="n">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="F111" t="n">
-        <v>46839.98</v>
+        <v>165862.58</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>9342.35</v>
       </c>
       <c r="H111" t="n">
-        <v>31707.06</v>
+        <v>141343.76</v>
       </c>
       <c r="I111" t="n">
-        <v>46839.98</v>
+        <v>156520.23</v>
       </c>
       <c r="J111" t="n">
-        <v>46839.98</v>
+        <v>156520.23</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E112" t="n">
-        <v>8900</v>
+        <v>580</v>
       </c>
       <c r="F112" t="n">
-        <v>1015466.78</v>
+        <v>313696.62</v>
       </c>
       <c r="G112" t="n">
-        <v>26748.39</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>673174.61</v>
+        <v>259611</v>
       </c>
       <c r="I112" t="n">
-        <v>988718.39</v>
+        <v>313696.62</v>
       </c>
       <c r="J112" t="n">
-        <v>988718.39</v>
+        <v>313696.62</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E113" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F113" t="n">
-        <v>1282694.88</v>
+        <v>1000584.04</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>33815.24</v>
       </c>
       <c r="H113" t="n">
-        <v>850325.8199999999</v>
+        <v>865369.98</v>
       </c>
       <c r="I113" t="n">
-        <v>1282694.88</v>
+        <v>966768.8</v>
       </c>
       <c r="J113" t="n">
-        <v>1282694.88</v>
+        <v>966768.8</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E114" t="n">
-        <v>1200</v>
+        <v>280</v>
       </c>
       <c r="F114" t="n">
-        <v>93679.96000000001</v>
+        <v>40383.93</v>
       </c>
       <c r="G114" t="n">
-        <v>2467.62</v>
+        <v>909.86</v>
       </c>
       <c r="H114" t="n">
-        <v>64014.64</v>
+        <v>33893.66</v>
       </c>
       <c r="I114" t="n">
-        <v>91212.34</v>
+        <v>39474.07</v>
       </c>
       <c r="J114" t="n">
-        <v>91212.34</v>
+        <v>39474.07</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E115" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F115" t="n">
-        <v>23419.99</v>
+        <v>600350.4300000001</v>
       </c>
       <c r="G115" t="n">
-        <v>411.27</v>
+        <v>13526.1</v>
       </c>
       <c r="H115" t="n">
-        <v>15853.53</v>
+        <v>519221.99</v>
       </c>
       <c r="I115" t="n">
-        <v>23008.72</v>
+        <v>586824.33</v>
       </c>
       <c r="J115" t="n">
-        <v>23008.72</v>
+        <v>586824.33</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E116" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="F116" t="n">
-        <v>97583.3</v>
+        <v>161535.73</v>
       </c>
       <c r="G116" t="n">
-        <v>4284.07</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>66056.38</v>
+        <v>135574.63</v>
       </c>
       <c r="I116" t="n">
-        <v>93299.23</v>
+        <v>161535.73</v>
       </c>
       <c r="J116" t="n">
-        <v>93299.23</v>
+        <v>161535.73</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4977,37 +4977,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="F117" t="n">
-        <v>50443.06</v>
+        <v>389416.49</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>33628.7</v>
+        <v>335330.87</v>
       </c>
       <c r="I117" t="n">
-        <v>50443.06</v>
+        <v>389416.49</v>
       </c>
       <c r="J117" t="n">
-        <v>50443.06</v>
+        <v>389416.49</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E118" t="n">
-        <v>1850</v>
+        <v>1150</v>
       </c>
       <c r="F118" t="n">
-        <v>244408.62</v>
+        <v>497587.74</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>165140.96</v>
+        <v>424031.29</v>
       </c>
       <c r="I118" t="n">
-        <v>244408.62</v>
+        <v>497587.74</v>
       </c>
       <c r="J118" t="n">
-        <v>244408.62</v>
+        <v>497587.74</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E119" t="n">
-        <v>21500</v>
+        <v>420</v>
       </c>
       <c r="F119" t="n">
-        <v>2840424.53</v>
+        <v>272591.55</v>
       </c>
       <c r="G119" t="n">
-        <v>74819.57000000001</v>
+        <v>15353.95</v>
       </c>
       <c r="H119" t="n">
-        <v>1876001.32</v>
+        <v>227159.62</v>
       </c>
       <c r="I119" t="n">
-        <v>2765604.96</v>
+        <v>257237.6</v>
       </c>
       <c r="J119" t="n">
-        <v>2765604.96</v>
+        <v>257237.6</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E120" t="n">
-        <v>21500</v>
+        <v>280</v>
       </c>
       <c r="F120" t="n">
-        <v>1807542.88</v>
+        <v>40383.93</v>
       </c>
       <c r="G120" t="n">
-        <v>31741.64</v>
+        <v>1364.8</v>
       </c>
       <c r="H120" t="n">
-        <v>1193819.02</v>
+        <v>33893.66</v>
       </c>
       <c r="I120" t="n">
-        <v>1775801.24</v>
+        <v>39019.13</v>
       </c>
       <c r="J120" t="n">
-        <v>1775801.24</v>
+        <v>39019.13</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E121" t="n">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="F121" t="n">
-        <v>302658.34</v>
+        <v>1817276.97</v>
       </c>
       <c r="G121" t="n">
-        <v>7972.32</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>201772.23</v>
+        <v>1564877.39</v>
       </c>
       <c r="I121" t="n">
-        <v>294686.02</v>
+        <v>1817276.97</v>
       </c>
       <c r="J121" t="n">
-        <v>294686.02</v>
+        <v>1817276.97</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,37 +5172,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E122" t="n">
-        <v>15400</v>
+        <v>420</v>
       </c>
       <c r="F122" t="n">
-        <v>2034536.64</v>
+        <v>151439.75</v>
       </c>
       <c r="G122" t="n">
-        <v>89319.49000000001</v>
+        <v>3411.99</v>
       </c>
       <c r="H122" t="n">
-        <v>1294705.14</v>
+        <v>126199.79</v>
       </c>
       <c r="I122" t="n">
-        <v>1945217.15</v>
+        <v>148027.76</v>
       </c>
       <c r="J122" t="n">
-        <v>1945217.15</v>
+        <v>148027.76</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5211,37 +5211,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E123" t="n">
-        <v>15400</v>
+        <v>420</v>
       </c>
       <c r="F123" t="n">
-        <v>184957.88</v>
+        <v>257447.57</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>117700.47</v>
+        <v>214539.64</v>
       </c>
       <c r="I123" t="n">
-        <v>184957.88</v>
+        <v>257447.57</v>
       </c>
       <c r="J123" t="n">
-        <v>184957.88</v>
+        <v>257447.57</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,37 +5250,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E124" t="n">
-        <v>1850</v>
+        <v>280</v>
       </c>
       <c r="F124" t="n">
-        <v>11109.48</v>
+        <v>161535.73</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>7506.41</v>
+        <v>135574.63</v>
       </c>
       <c r="I124" t="n">
-        <v>11109.48</v>
+        <v>161535.73</v>
       </c>
       <c r="J124" t="n">
-        <v>11109.48</v>
+        <v>161535.73</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,37 +5289,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E125" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F125" t="n">
-        <v>180153.78</v>
+        <v>1200700.85</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>27052.19</v>
       </c>
       <c r="H125" t="n">
-        <v>123105.08</v>
+        <v>1038443.98</v>
       </c>
       <c r="I125" t="n">
-        <v>180153.78</v>
+        <v>1173648.66</v>
       </c>
       <c r="J125" t="n">
-        <v>180153.78</v>
+        <v>1173648.66</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E126" t="n">
-        <v>15400</v>
+        <v>3600</v>
       </c>
       <c r="F126" t="n">
-        <v>924789.38</v>
+        <v>1168249.48</v>
       </c>
       <c r="G126" t="n">
-        <v>16239.91</v>
+        <v>65802.63</v>
       </c>
       <c r="H126" t="n">
-        <v>588502.33</v>
+        <v>1005992.61</v>
       </c>
       <c r="I126" t="n">
-        <v>908549.47</v>
+        <v>1102446.85</v>
       </c>
       <c r="J126" t="n">
-        <v>908549.47</v>
+        <v>1102446.85</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E127" t="n">
-        <v>1850</v>
+        <v>3600</v>
       </c>
       <c r="F127" t="n">
-        <v>177751.73</v>
+        <v>1817276.97</v>
       </c>
       <c r="G127" t="n">
-        <v>4682.16</v>
+        <v>102359.65</v>
       </c>
       <c r="H127" t="n">
-        <v>120102.52</v>
+        <v>1564877.39</v>
       </c>
       <c r="I127" t="n">
-        <v>173069.57</v>
+        <v>1714917.32</v>
       </c>
       <c r="J127" t="n">
-        <v>173069.57</v>
+        <v>1714917.32</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E128" t="n">
-        <v>8900</v>
+        <v>420</v>
       </c>
       <c r="F128" t="n">
-        <v>694793.0600000001</v>
+        <v>136295.77</v>
       </c>
       <c r="G128" t="n">
-        <v>30502.55</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>460593.15</v>
+        <v>113579.81</v>
       </c>
       <c r="I128" t="n">
-        <v>664290.51</v>
+        <v>136295.77</v>
       </c>
       <c r="J128" t="n">
-        <v>664290.51</v>
+        <v>136295.77</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E129" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F129" t="n">
-        <v>122504.57</v>
+        <v>667056.03</v>
       </c>
       <c r="G129" t="n">
-        <v>5378.15</v>
+        <v>15029</v>
       </c>
       <c r="H129" t="n">
-        <v>83711.45</v>
+        <v>576913.3199999999</v>
       </c>
       <c r="I129" t="n">
-        <v>117126.42</v>
+        <v>652027.03</v>
       </c>
       <c r="J129" t="n">
-        <v>117126.42</v>
+        <v>652027.03</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E130" t="n">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="F130" t="n">
-        <v>11710</v>
+        <v>248793.87</v>
       </c>
       <c r="G130" t="n">
-        <v>308.45</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>7926.77</v>
+        <v>212015.65</v>
       </c>
       <c r="I130" t="n">
-        <v>11401.55</v>
+        <v>248793.87</v>
       </c>
       <c r="J130" t="n">
-        <v>11401.55</v>
+        <v>248793.87</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,37 +5523,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E131" t="n">
-        <v>1850</v>
+        <v>1150</v>
       </c>
       <c r="F131" t="n">
-        <v>155532.76</v>
+        <v>207328.23</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>105089.7</v>
+        <v>176679.71</v>
       </c>
       <c r="I131" t="n">
-        <v>155532.76</v>
+        <v>207328.23</v>
       </c>
       <c r="J131" t="n">
-        <v>155532.76</v>
+        <v>207328.23</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,37 +5562,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E132" t="n">
-        <v>4200</v>
+        <v>280</v>
       </c>
       <c r="F132" t="n">
-        <v>277436.81</v>
+        <v>171631.71</v>
       </c>
       <c r="G132" t="n">
-        <v>12179.93</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>184957.88</v>
+        <v>144048.05</v>
       </c>
       <c r="I132" t="n">
-        <v>265256.88</v>
+        <v>171631.71</v>
       </c>
       <c r="J132" t="n">
-        <v>265256.88</v>
+        <v>171631.71</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E133" t="n">
-        <v>2400</v>
+        <v>580</v>
       </c>
       <c r="F133" t="n">
-        <v>331482.95</v>
+        <v>313696.62</v>
       </c>
       <c r="G133" t="n">
-        <v>8731.59</v>
+        <v>7067.69</v>
       </c>
       <c r="H133" t="n">
-        <v>207176.84</v>
+        <v>259611</v>
       </c>
       <c r="I133" t="n">
-        <v>322751.36</v>
+        <v>306628.93</v>
       </c>
       <c r="J133" t="n">
-        <v>322751.36</v>
+        <v>306628.93</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E134" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F134" t="n">
-        <v>327879.87</v>
+        <v>667056.03</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>15029</v>
       </c>
       <c r="H134" t="n">
-        <v>218586.58</v>
+        <v>576913.3199999999</v>
       </c>
       <c r="I134" t="n">
-        <v>327879.87</v>
+        <v>652027.03</v>
       </c>
       <c r="J134" t="n">
-        <v>327879.87</v>
+        <v>652027.03</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E135" t="n">
-        <v>8900</v>
+        <v>1150</v>
       </c>
       <c r="F135" t="n">
-        <v>1068912.4</v>
+        <v>207328.23</v>
       </c>
       <c r="G135" t="n">
-        <v>28156.2</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>708604.85</v>
+        <v>176679.71</v>
       </c>
       <c r="I135" t="n">
-        <v>1040756.2</v>
+        <v>207328.23</v>
       </c>
       <c r="J135" t="n">
-        <v>1040756.2</v>
+        <v>207328.23</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,12 +5718,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -5733,22 +5733,22 @@
         <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="F136" t="n">
-        <v>11710</v>
+        <v>30287.95</v>
       </c>
       <c r="G136" t="n">
-        <v>308.45</v>
+        <v>682.4</v>
       </c>
       <c r="H136" t="n">
-        <v>7926.77</v>
+        <v>25420.24</v>
       </c>
       <c r="I136" t="n">
-        <v>11401.55</v>
+        <v>29605.55</v>
       </c>
       <c r="J136" t="n">
-        <v>11401.55</v>
+        <v>29605.55</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5757,37 +5757,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E137" t="n">
-        <v>4200</v>
+        <v>280</v>
       </c>
       <c r="F137" t="n">
-        <v>201772.23</v>
+        <v>141343.76</v>
       </c>
       <c r="G137" t="n">
-        <v>5314.88</v>
+        <v>4776.78</v>
       </c>
       <c r="H137" t="n">
-        <v>134514.82</v>
+        <v>118627.8</v>
       </c>
       <c r="I137" t="n">
-        <v>196457.35</v>
+        <v>136566.98</v>
       </c>
       <c r="J137" t="n">
-        <v>196457.35</v>
+        <v>136566.98</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5796,37 +5796,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E138" t="n">
-        <v>2400</v>
+        <v>580</v>
       </c>
       <c r="F138" t="n">
-        <v>245009.14</v>
+        <v>188217.97</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>153130.71</v>
+        <v>155766.6</v>
       </c>
       <c r="I138" t="n">
-        <v>245009.14</v>
+        <v>188217.97</v>
       </c>
       <c r="J138" t="n">
-        <v>245009.14</v>
+        <v>188217.97</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5835,37 +5835,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E139" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F139" t="n">
-        <v>2219494.52</v>
+        <v>933878.4399999999</v>
       </c>
       <c r="G139" t="n">
-        <v>38975.78</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>1412405.6</v>
+        <v>807678.65</v>
       </c>
       <c r="I139" t="n">
-        <v>2180518.74</v>
+        <v>933878.4399999999</v>
       </c>
       <c r="J139" t="n">
-        <v>2180518.74</v>
+        <v>933878.4399999999</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5874,37 +5874,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E140" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="F140" t="n">
-        <v>97583.3</v>
+        <v>191823.68</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>6482.78</v>
       </c>
       <c r="H140" t="n">
-        <v>66056.38</v>
+        <v>160994.87</v>
       </c>
       <c r="I140" t="n">
-        <v>97583.3</v>
+        <v>185340.9</v>
       </c>
       <c r="J140" t="n">
-        <v>97583.3</v>
+        <v>185340.9</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5913,37 +5913,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E141" t="n">
-        <v>4200</v>
+        <v>1150</v>
       </c>
       <c r="F141" t="n">
-        <v>428765.99</v>
+        <v>331725.16</v>
       </c>
       <c r="G141" t="n">
-        <v>18823.53</v>
+        <v>11210.82</v>
       </c>
       <c r="H141" t="n">
-        <v>285843.99</v>
+        <v>282687.53</v>
       </c>
       <c r="I141" t="n">
-        <v>409942.46</v>
+        <v>320514.34</v>
       </c>
       <c r="J141" t="n">
-        <v>409942.46</v>
+        <v>320514.34</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5952,37 +5952,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E142" t="n">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="F142" t="n">
-        <v>46839.98</v>
+        <v>290259.52</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>6539.64</v>
       </c>
       <c r="H142" t="n">
-        <v>31707.06</v>
+        <v>247351.59</v>
       </c>
       <c r="I142" t="n">
-        <v>46839.98</v>
+        <v>283719.88</v>
       </c>
       <c r="J142" t="n">
-        <v>46839.98</v>
+        <v>283719.88</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5991,12 +5991,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
@@ -6006,22 +6006,22 @@
         <v>5</v>
       </c>
       <c r="E143" t="n">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="F143" t="n">
-        <v>126107.64</v>
+        <v>649027.49</v>
       </c>
       <c r="G143" t="n">
-        <v>2214.53</v>
+        <v>14622.81</v>
       </c>
       <c r="H143" t="n">
-        <v>84071.75999999999</v>
+        <v>558884.78</v>
       </c>
       <c r="I143" t="n">
-        <v>123893.11</v>
+        <v>634404.6800000001</v>
       </c>
       <c r="J143" t="n">
-        <v>123893.11</v>
+        <v>634404.6800000001</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6030,37 +6030,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E144" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F144" t="n">
-        <v>1068912.4</v>
+        <v>266822.41</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>708604.85</v>
+        <v>230765.33</v>
       </c>
       <c r="I144" t="n">
-        <v>1068912.4</v>
+        <v>266822.41</v>
       </c>
       <c r="J144" t="n">
-        <v>1068912.4</v>
+        <v>266822.41</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6069,37 +6069,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E145" t="n">
-        <v>4200</v>
+        <v>280</v>
       </c>
       <c r="F145" t="n">
-        <v>151329.17</v>
+        <v>141343.76</v>
       </c>
       <c r="G145" t="n">
-        <v>3986.16</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>100886.11</v>
+        <v>118627.8</v>
       </c>
       <c r="I145" t="n">
-        <v>147343.01</v>
+        <v>141343.76</v>
       </c>
       <c r="J145" t="n">
-        <v>147343.01</v>
+        <v>141343.76</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6108,37 +6108,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E146" t="n">
-        <v>21500</v>
+        <v>580</v>
       </c>
       <c r="F146" t="n">
-        <v>2840424.53</v>
+        <v>376435.94</v>
       </c>
       <c r="G146" t="n">
-        <v>124699.29</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>1876001.32</v>
+        <v>311533.19</v>
       </c>
       <c r="I146" t="n">
-        <v>2715725.24</v>
+        <v>376435.94</v>
       </c>
       <c r="J146" t="n">
-        <v>2715725.24</v>
+        <v>376435.94</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6147,37 +6147,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E147" t="n">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="F147" t="n">
-        <v>81969.97</v>
+        <v>539053.39</v>
       </c>
       <c r="G147" t="n">
-        <v>1439.45</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>55487.36</v>
+        <v>459367.23</v>
       </c>
       <c r="I147" t="n">
-        <v>80530.52</v>
+        <v>539053.39</v>
       </c>
       <c r="J147" t="n">
-        <v>80530.52</v>
+        <v>539053.39</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E148" t="n">
-        <v>21500</v>
+        <v>1150</v>
       </c>
       <c r="F148" t="n">
-        <v>387330.62</v>
+        <v>621984.6800000001</v>
       </c>
       <c r="G148" t="n">
-        <v>10202.67</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>255818.36</v>
+        <v>530039.12</v>
       </c>
       <c r="I148" t="n">
-        <v>377127.95</v>
+        <v>621984.6800000001</v>
       </c>
       <c r="J148" t="n">
-        <v>377127.95</v>
+        <v>621984.6800000001</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -6225,37 +6225,37 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E149" t="n">
-        <v>15400</v>
+        <v>420</v>
       </c>
       <c r="F149" t="n">
-        <v>832310.4399999999</v>
+        <v>212015.65</v>
       </c>
       <c r="G149" t="n">
-        <v>36539.79</v>
+        <v>11941.96</v>
       </c>
       <c r="H149" t="n">
-        <v>529652.1</v>
+        <v>176679.71</v>
       </c>
       <c r="I149" t="n">
-        <v>795770.65</v>
+        <v>200073.69</v>
       </c>
       <c r="J149" t="n">
-        <v>795770.65</v>
+        <v>200073.69</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -6264,37 +6264,37 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E150" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="F150" t="n">
-        <v>66356.64</v>
+        <v>141343.76</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>3184.52</v>
       </c>
       <c r="H150" t="n">
-        <v>44918.34</v>
+        <v>118627.8</v>
       </c>
       <c r="I150" t="n">
-        <v>66356.64</v>
+        <v>138159.24</v>
       </c>
       <c r="J150" t="n">
-        <v>66356.64</v>
+        <v>138159.24</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -6303,37 +6303,37 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>21500</v>
+        <v>580</v>
       </c>
       <c r="F151" t="n">
-        <v>1936653.09</v>
+        <v>20913.11</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>471.18</v>
       </c>
       <c r="H151" t="n">
-        <v>1279091.81</v>
+        <v>17307.4</v>
       </c>
       <c r="I151" t="n">
-        <v>1936653.09</v>
+        <v>20441.93</v>
       </c>
       <c r="J151" t="n">
-        <v>1936653.09</v>
+        <v>20441.93</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -6342,37 +6342,37 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E152" t="n">
-        <v>650</v>
+        <v>3600</v>
       </c>
       <c r="F152" t="n">
-        <v>39033.32</v>
+        <v>2596109.95</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>87736.84</v>
       </c>
       <c r="H152" t="n">
-        <v>26422.55</v>
+        <v>2235539.13</v>
       </c>
       <c r="I152" t="n">
-        <v>39033.32</v>
+        <v>2508373.11</v>
       </c>
       <c r="J152" t="n">
-        <v>39033.32</v>
+        <v>2508373.11</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -6381,37 +6381,37 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E153" t="n">
-        <v>4200</v>
+        <v>1150</v>
       </c>
       <c r="F153" t="n">
-        <v>504430.57</v>
+        <v>580519.03</v>
       </c>
       <c r="G153" t="n">
-        <v>22145.33</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>336287.05</v>
+        <v>494703.17</v>
       </c>
       <c r="I153" t="n">
-        <v>482285.24</v>
+        <v>580519.03</v>
       </c>
       <c r="J153" t="n">
-        <v>482285.24</v>
+        <v>580519.03</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -6420,1093 +6420,1093 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E154" t="n">
-        <v>2400</v>
+        <v>580</v>
       </c>
       <c r="F154" t="n">
-        <v>216184.53</v>
+        <v>397349.05</v>
       </c>
       <c r="G154" t="n">
-        <v>9490.860000000001</v>
+        <v>13428.61</v>
       </c>
       <c r="H154" t="n">
-        <v>135115.33</v>
+        <v>328840.59</v>
       </c>
       <c r="I154" t="n">
-        <v>206693.67</v>
+        <v>383920.44</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>115176.13</v>
       </c>
       <c r="K154" t="n">
-        <v>206693.67</v>
+        <v>268744.31</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E155" t="n">
-        <v>1850</v>
+        <v>580</v>
       </c>
       <c r="F155" t="n">
-        <v>166642.24</v>
+        <v>209131.08</v>
       </c>
       <c r="G155" t="n">
-        <v>7315.87</v>
+        <v>4711.79</v>
       </c>
       <c r="H155" t="n">
-        <v>112596.11</v>
+        <v>173074</v>
       </c>
       <c r="I155" t="n">
-        <v>159326.37</v>
+        <v>204419.29</v>
       </c>
       <c r="J155" t="n">
-        <v>79663.17999999999</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>79663.19</v>
+        <v>204419.29</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kurumsal Müşteri D - Anadolu</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E156" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F156" t="n">
-        <v>79267.66</v>
+        <v>400233.62</v>
       </c>
       <c r="G156" t="n">
-        <v>3479.98</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>54166.24</v>
+        <v>346147.99</v>
       </c>
       <c r="I156" t="n">
-        <v>75787.67999999999</v>
+        <v>400233.62</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>200116.81</v>
       </c>
       <c r="K156" t="n">
-        <v>75787.67999999999</v>
+        <v>200116.81</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E157" t="n">
-        <v>8900</v>
+        <v>420</v>
       </c>
       <c r="F157" t="n">
-        <v>106891.24</v>
+        <v>257447.57</v>
       </c>
       <c r="G157" t="n">
-        <v>2815.62</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>70860.49000000001</v>
+        <v>214539.64</v>
       </c>
       <c r="I157" t="n">
-        <v>104075.62</v>
+        <v>257447.57</v>
       </c>
       <c r="J157" t="n">
-        <v>31222.69</v>
+        <v>128723.79</v>
       </c>
       <c r="K157" t="n">
-        <v>72852.92999999999</v>
+        <v>128723.78</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E158" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F158" t="n">
-        <v>89776.63</v>
+        <v>333528.01</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>60771.87</v>
+        <v>288456.66</v>
       </c>
       <c r="I158" t="n">
-        <v>89776.63</v>
+        <v>333528.01</v>
       </c>
       <c r="J158" t="n">
-        <v>26932.99</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>62843.64</v>
+        <v>333528.01</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ayçiçek Yağı 5L Koli (4 Adet)</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E159" t="n">
-        <v>8900</v>
+        <v>980</v>
       </c>
       <c r="F159" t="n">
-        <v>106891.24</v>
+        <v>318023.47</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>70860.49000000001</v>
+        <v>272591.55</v>
       </c>
       <c r="I159" t="n">
-        <v>106891.24</v>
+        <v>318023.47</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>95407.03999999999</v>
       </c>
       <c r="K159" t="n">
-        <v>106891.24</v>
+        <v>222616.43</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E160" t="n">
-        <v>21500</v>
+        <v>420</v>
       </c>
       <c r="F160" t="n">
-        <v>1936653.09</v>
+        <v>75719.87</v>
       </c>
       <c r="G160" t="n">
-        <v>85022.24000000001</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>1279091.81</v>
+        <v>63099.89</v>
       </c>
       <c r="I160" t="n">
-        <v>1851630.85</v>
+        <v>75719.87</v>
       </c>
       <c r="J160" t="n">
-        <v>555489.26</v>
+        <v>22715.96</v>
       </c>
       <c r="K160" t="n">
-        <v>1296141.59</v>
+        <v>53003.91</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E161" t="n">
-        <v>8900</v>
+        <v>3600</v>
       </c>
       <c r="F161" t="n">
-        <v>641347.4399999999</v>
+        <v>2076887.96</v>
       </c>
       <c r="G161" t="n">
-        <v>11262.48</v>
+        <v>70189.47</v>
       </c>
       <c r="H161" t="n">
-        <v>425162.91</v>
+        <v>1788431.3</v>
       </c>
       <c r="I161" t="n">
-        <v>630084.96</v>
+        <v>2006698.49</v>
       </c>
       <c r="J161" t="n">
-        <v>315042.48</v>
+        <v>1003349.24</v>
       </c>
       <c r="K161" t="n">
-        <v>315042.48</v>
+        <v>1003349.25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E162" t="n">
-        <v>15400</v>
+        <v>280</v>
       </c>
       <c r="F162" t="n">
-        <v>1202226.2</v>
+        <v>191823.68</v>
       </c>
       <c r="G162" t="n">
-        <v>31667.82</v>
+        <v>10804.63</v>
       </c>
       <c r="H162" t="n">
-        <v>765053.03</v>
+        <v>160994.87</v>
       </c>
       <c r="I162" t="n">
-        <v>1170558.38</v>
+        <v>181019.05</v>
       </c>
       <c r="J162" t="n">
-        <v>585279.1899999999</v>
+        <v>90509.52</v>
       </c>
       <c r="K162" t="n">
-        <v>585279.1899999999</v>
+        <v>90509.53</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E163" t="n">
-        <v>650</v>
+        <v>3600</v>
       </c>
       <c r="F163" t="n">
-        <v>85873.3</v>
+        <v>1427860.47</v>
       </c>
       <c r="G163" t="n">
-        <v>3769.98</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>58129.62</v>
+        <v>1229546.52</v>
       </c>
       <c r="I163" t="n">
-        <v>82103.32000000001</v>
+        <v>1427860.47</v>
       </c>
       <c r="J163" t="n">
-        <v>24631</v>
+        <v>713930.23</v>
       </c>
       <c r="K163" t="n">
-        <v>57472.32</v>
+        <v>713930.24</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E164" t="n">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="F164" t="n">
-        <v>11710</v>
+        <v>663450.3199999999</v>
       </c>
       <c r="G164" t="n">
-        <v>205.64</v>
+        <v>22421.64</v>
       </c>
       <c r="H164" t="n">
-        <v>7926.77</v>
+        <v>565375.0600000001</v>
       </c>
       <c r="I164" t="n">
-        <v>11504.36</v>
+        <v>641028.6800000001</v>
       </c>
       <c r="J164" t="n">
-        <v>3451.31</v>
+        <v>192308.6</v>
       </c>
       <c r="K164" t="n">
-        <v>8053.05</v>
+        <v>448720.08</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E165" t="n">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="F165" t="n">
-        <v>144123.02</v>
+        <v>1168249.48</v>
       </c>
       <c r="G165" t="n">
-        <v>2530.89</v>
+        <v>65802.63</v>
       </c>
       <c r="H165" t="n">
-        <v>90076.89</v>
+        <v>1005992.61</v>
       </c>
       <c r="I165" t="n">
-        <v>141592.13</v>
+        <v>1102446.85</v>
       </c>
       <c r="J165" t="n">
-        <v>42477.64</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>99114.49000000001</v>
+        <v>1102446.85</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E166" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F166" t="n">
-        <v>587901.8199999999</v>
+        <v>1133995.25</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>389732.67</v>
+        <v>980752.65</v>
       </c>
       <c r="I166" t="n">
-        <v>587901.8199999999</v>
+        <v>1133995.25</v>
       </c>
       <c r="J166" t="n">
-        <v>176370.55</v>
+        <v>566997.62</v>
       </c>
       <c r="K166" t="n">
-        <v>411531.27</v>
+        <v>566997.63</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E167" t="n">
-        <v>8900</v>
+        <v>580</v>
       </c>
       <c r="F167" t="n">
-        <v>641347.4399999999</v>
+        <v>313696.62</v>
       </c>
       <c r="G167" t="n">
-        <v>11262.48</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>425162.91</v>
+        <v>259611</v>
       </c>
       <c r="I167" t="n">
-        <v>630084.96</v>
+        <v>313696.62</v>
       </c>
       <c r="J167" t="n">
-        <v>315042.48</v>
+        <v>156848.31</v>
       </c>
       <c r="K167" t="n">
-        <v>315042.48</v>
+        <v>156848.31</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E168" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F168" t="n">
-        <v>72061.50999999999</v>
+        <v>667056.03</v>
       </c>
       <c r="G168" t="n">
-        <v>3163.62</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>45038.44</v>
+        <v>576913.3199999999</v>
       </c>
       <c r="I168" t="n">
-        <v>68897.89</v>
+        <v>667056.03</v>
       </c>
       <c r="J168" t="n">
-        <v>34448.94</v>
+        <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>34448.95</v>
+        <v>667056.03</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu B - Anadolu</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E169" t="n">
-        <v>4200</v>
+        <v>420</v>
       </c>
       <c r="F169" t="n">
-        <v>252215.29</v>
+        <v>302879.49</v>
       </c>
       <c r="G169" t="n">
-        <v>11072.66</v>
+        <v>17059.94</v>
       </c>
       <c r="H169" t="n">
-        <v>168143.52</v>
+        <v>252399.58</v>
       </c>
       <c r="I169" t="n">
-        <v>241142.63</v>
+        <v>285819.55</v>
       </c>
       <c r="J169" t="n">
-        <v>72342.78999999999</v>
+        <v>85745.86</v>
       </c>
       <c r="K169" t="n">
-        <v>168799.84</v>
+        <v>200073.69</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E170" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="F170" t="n">
-        <v>19516.66</v>
+        <v>397349.05</v>
       </c>
       <c r="G170" t="n">
-        <v>856.8099999999999</v>
+        <v>22381.02</v>
       </c>
       <c r="H170" t="n">
-        <v>13211.28</v>
+        <v>328840.59</v>
       </c>
       <c r="I170" t="n">
-        <v>18659.85</v>
+        <v>374968.03</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>187484.02</v>
       </c>
       <c r="K170" t="n">
-        <v>18659.85</v>
+        <v>187484.01</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E171" t="n">
-        <v>2400</v>
+        <v>580</v>
       </c>
       <c r="F171" t="n">
-        <v>245009.14</v>
+        <v>397349.05</v>
       </c>
       <c r="G171" t="n">
-        <v>4302.52</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>153130.71</v>
+        <v>328840.59</v>
       </c>
       <c r="I171" t="n">
-        <v>240706.62</v>
+        <v>397349.05</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>119204.71</v>
       </c>
       <c r="K171" t="n">
-        <v>240706.62</v>
+        <v>278144.34</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E172" t="n">
-        <v>650</v>
+        <v>420</v>
       </c>
       <c r="F172" t="n">
-        <v>39033.32</v>
+        <v>242303.6</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>13647.95</v>
       </c>
       <c r="H172" t="n">
-        <v>26422.55</v>
+        <v>201919.66</v>
       </c>
       <c r="I172" t="n">
-        <v>39033.32</v>
+        <v>228655.65</v>
       </c>
       <c r="J172" t="n">
-        <v>19516.66</v>
+        <v>114327.82</v>
       </c>
       <c r="K172" t="n">
-        <v>19516.66</v>
+        <v>114327.83</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D173" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E173" t="n">
-        <v>650</v>
+        <v>1150</v>
       </c>
       <c r="F173" t="n">
-        <v>97583.3</v>
+        <v>621984.6800000001</v>
       </c>
       <c r="G173" t="n">
-        <v>2570.44</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>66056.38</v>
+        <v>530039.12</v>
       </c>
       <c r="I173" t="n">
-        <v>95012.86</v>
+        <v>621984.6800000001</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>186595.4</v>
       </c>
       <c r="K173" t="n">
-        <v>95012.86</v>
+        <v>435389.28</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Rize Geleneksel Çay 1000g Koli</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E174" t="n">
-        <v>1200</v>
+        <v>280</v>
       </c>
       <c r="F174" t="n">
-        <v>36030.76</v>
+        <v>30287.95</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>1705.99</v>
       </c>
       <c r="H174" t="n">
-        <v>24621.02</v>
+        <v>25420.24</v>
       </c>
       <c r="I174" t="n">
-        <v>36030.76</v>
+        <v>28581.96</v>
       </c>
       <c r="J174" t="n">
-        <v>10809.23</v>
+        <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>25221.53</v>
+        <v>28581.96</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E175" t="n">
-        <v>15400</v>
+        <v>1150</v>
       </c>
       <c r="F175" t="n">
-        <v>369915.75</v>
+        <v>331725.16</v>
       </c>
       <c r="G175" t="n">
-        <v>16239.91</v>
+        <v>11210.82</v>
       </c>
       <c r="H175" t="n">
-        <v>235400.93</v>
+        <v>282687.53</v>
       </c>
       <c r="I175" t="n">
-        <v>353675.84</v>
+        <v>320514.34</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>160257.17</v>
       </c>
       <c r="K175" t="n">
-        <v>353675.84</v>
+        <v>160257.17</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ulusal Hesap H - Anadolu</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Domates Salçası 4500g Teneke</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E176" t="n">
-        <v>1850</v>
+        <v>420</v>
       </c>
       <c r="F176" t="n">
-        <v>244408.62</v>
+        <v>257447.57</v>
       </c>
       <c r="G176" t="n">
-        <v>4291.98</v>
+        <v>14500.95</v>
       </c>
       <c r="H176" t="n">
-        <v>165140.96</v>
+        <v>214539.64</v>
       </c>
       <c r="I176" t="n">
-        <v>240116.64</v>
+        <v>242946.62</v>
       </c>
       <c r="J176" t="n">
-        <v>120058.32</v>
+        <v>121473.31</v>
       </c>
       <c r="K176" t="n">
-        <v>120058.32</v>
+        <v>121473.31</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Bölge Bayi C - Anadolu</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E177" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F177" t="n">
-        <v>1068912.4</v>
+        <v>800467.24</v>
       </c>
       <c r="G177" t="n">
-        <v>28156.2</v>
+        <v>18034.8</v>
       </c>
       <c r="H177" t="n">
-        <v>708604.85</v>
+        <v>692295.99</v>
       </c>
       <c r="I177" t="n">
-        <v>1040756.2</v>
+        <v>782432.4399999999</v>
       </c>
       <c r="J177" t="n">
-        <v>312226.86</v>
+        <v>391216.22</v>
       </c>
       <c r="K177" t="n">
-        <v>728529.34</v>
+        <v>391216.22</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Anadolu</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Pilavlık Bulgur 25kg</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E178" t="n">
-        <v>8900</v>
+        <v>580</v>
       </c>
       <c r="F178" t="n">
-        <v>320673.72</v>
+        <v>230044.19</v>
       </c>
       <c r="G178" t="n">
-        <v>14078.1</v>
+        <v>12957.43</v>
       </c>
       <c r="H178" t="n">
-        <v>212581.46</v>
+        <v>190381.4</v>
       </c>
       <c r="I178" t="n">
-        <v>306595.62</v>
+        <v>217086.76</v>
       </c>
       <c r="J178" t="n">
-        <v>91978.69</v>
+        <v>108543.38</v>
       </c>
       <c r="K178" t="n">
-        <v>214616.93</v>
+        <v>108543.38</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu A - Anadolu</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Tam Yağlı Beyaz Peynir 17kg</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E179" t="n">
-        <v>8900</v>
+        <v>3600</v>
       </c>
       <c r="F179" t="n">
-        <v>1282694.88</v>
+        <v>1427860.47</v>
       </c>
       <c r="G179" t="n">
-        <v>33787.44</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>850325.8199999999</v>
+        <v>1229546.52</v>
       </c>
       <c r="I179" t="n">
-        <v>1248907.44</v>
+        <v>1427860.47</v>
       </c>
       <c r="J179" t="n">
-        <v>624453.72</v>
+        <v>713930.23</v>
       </c>
       <c r="K179" t="n">
-        <v>624453.72</v>
+        <v>713930.24</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Anadolu</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Osmancık Baldo Pirinç 25kg</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E180" t="n">
-        <v>2400</v>
+        <v>1150</v>
       </c>
       <c r="F180" t="n">
-        <v>172947.62</v>
+        <v>746381.61</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>25224.34</v>
       </c>
       <c r="H180" t="n">
-        <v>108092.27</v>
+        <v>636046.9399999999</v>
       </c>
       <c r="I180" t="n">
-        <v>172947.62</v>
+        <v>721157.27</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>172947.62</v>
+        <v>721157.27</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - Anadolu</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kristal Toz Şeker 50kg Torba</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E181" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F181" t="n">
-        <v>2311973.46</v>
+        <v>1334112.06</v>
       </c>
       <c r="G181" t="n">
-        <v>60899.65</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>1471255.84</v>
+        <v>1153826.65</v>
       </c>
       <c r="I181" t="n">
-        <v>2251073.81</v>
+        <v>1334112.06</v>
       </c>
       <c r="J181" t="n">
-        <v>1125536.91</v>
+        <v>667056.03</v>
       </c>
       <c r="K181" t="n">
-        <v>1125536.9</v>
+        <v>667056.03</v>
       </c>
     </row>
   </sheetData>
